--- a/tame_output/ON/bt/strategyON_20240508.xlsx
+++ b/tame_output/ON/bt/strategyON_20240508.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>54.1%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.8%</t>
+          <t>-79.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>114.9%</t>
+          <t>113.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>135.5%</t>
+          <t>134.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.4%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.0%</t>
+          <t>-56.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.4%</t>
+          <t>-76.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>95.2%</t>
+          <t>94.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>440.4%</t>
+          <t>444.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>-9.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-606.1%</t>
+          <t>-605.9%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,27 +1150,27 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-44.5%</t>
+          <t>-44.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>-1.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-77.2%</t>
+          <t>-52.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-280.8%</t>
+          <t>-280.7%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-29.6%</t>
+          <t>-30.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-23.4%</t>
+          <t>-24.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-155.5%</t>
+          <t>-156.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-261.7%</t>
+          <t>-268.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-195.4%</t>
+          <t>-199.2%</t>
         </is>
       </c>
     </row>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.999029684386291</v>
+        <v>-7.838602165915842</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.08108960437557489</v>
+        <v>-0.01691859698739551</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.741209520764524</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094119</v>
+        <v>3.374439043094118</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.344904506371099</v>
+        <v>-8.18447698790065</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.2233399680238031</v>
+        <v>-0.1591689606356237</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.741209520764524</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199289</v>
+        <v>3.405960511199288</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.507046776834192</v>
+        <v>-8.346619258363743</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2897919561540396</v>
+        <v>-0.2256209487658598</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.741209520764524</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.803708118644391</v>
+        <v>-8.643280600173942</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.4046775169489107</v>
+        <v>-0.3405065095607309</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.809952656498403</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392309</v>
+        <v>3.419979433923089</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.237057226754626</v>
+        <v>-9.076629708284177</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.5820434647274078</v>
+        <v>-0.5178724573392284</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.809952656498403</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297753</v>
+        <v>3.458100091297752</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.620058615497257</v>
+        <v>-9.459631097026808</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.7353461215460442</v>
+        <v>-0.6711751141578648</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.809952656498403</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131762</v>
+        <v>3.447750501317619</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.777457495710378</v>
+        <v>-9.617029977239929</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.7957341576598624</v>
+        <v>-0.7315631502716831</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.967351536711524</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737174</v>
+        <v>3.503515506737173</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.13698781821438</v>
+        <v>-9.97656029974393</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.9341959833634128</v>
+        <v>-0.8700249759752334</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.967351536711524</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.46338784687939</v>
+        <v>-10.30296032840894</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.05683997487224</v>
+        <v>-0.9926689674840614</v>
       </c>
       <c r="F1875" t="n">
         <v>-2.293751565376537</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50044609677668</v>
+        <v>3.500446096776679</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.68253681495359</v>
+        <v>-10.52210929648314</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.141457811480151</v>
+        <v>-1.077286804091971</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.512900533450734</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.67884588999718</v>
+        <v>-10.51841837152673</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.139981441497586</v>
+        <v>-1.075810434109407</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.512900533450734</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611698</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.88310406532704</v>
+        <v>-10.72267654685659</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.21617151451089</v>
+        <v>-1.15200050712271</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.640539478064723</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199889</v>
+        <v>3.496848329199888</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.10114183695822</v>
+        <v>-10.94071431848777</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.298904068678925</v>
+        <v>-1.234733061290745</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.815310246160622</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910632</v>
+        <v>3.499968163910631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.02767200529077</v>
+        <v>-10.86724448682032</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.254144434518524</v>
+        <v>-1.189973427130345</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.741840414493173</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.20279642267731</v>
+        <v>-11.04236890420687</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.309638980725625</v>
+        <v>-1.245467973337445</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.916964831879717</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.48587501888027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.4372485166918</v>
+        <v>-11.27682099822136</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.410638983233016</v>
+        <v>-1.346467975844837</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.916964831879717</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234397</v>
+        <v>3.480688917234396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.72505236122904</v>
+        <v>-11.56462484275859</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.532432711821888</v>
+        <v>-1.468261704433708</v>
       </c>
       <c r="F1883" t="n">
         <v>-3.204768676416955</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.493712438860585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.95487680839287</v>
+        <v>-11.79444928992242</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.623246700848862</v>
+        <v>-1.559075693460682</v>
       </c>
       <c r="F1884" t="n">
         <v>-3.367416213487116</v>
@@ -44906,10 +44906,10 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.18690572812913</v>
+        <v>-12.02647820965868</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.713364540114252</v>
+        <v>-1.649193532726072</v>
       </c>
       <c r="F1885" t="n">
         <v>-3.429428910675539</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.13489021416032</v>
+        <v>-11.97446269568987</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.688567998840326</v>
+        <v>-1.624396991452146</v>
       </c>
       <c r="F1886" t="n">
         <v>-3.429428910675539</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.60003468962892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.27656205588444</v>
+        <v>-12.11613453741399</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.746711962428716</v>
+        <v>-1.682540955040536</v>
       </c>
       <c r="F1887" t="n">
         <v>-3.429428910675539</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410718</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.2269712114596</v>
+        <v>-12.06654369298915</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.71182221449391</v>
+        <v>-1.64765120710573</v>
       </c>
       <c r="F1888" t="n">
         <v>-3.379838066250705</v>
@@ -44998,10 +44998,10 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.0278191042225</v>
+        <v>-11.86739158575205</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.645212505245753</v>
+        <v>-1.581041497857573</v>
       </c>
       <c r="F1889" t="n">
         <v>-3.214515540300892</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085281</v>
+        <v>3.68515780608528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.80197395150309</v>
+        <v>-11.64154643303264</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.54529537112178</v>
+        <v>-1.4811243637336</v>
       </c>
       <c r="F1890" t="n">
         <v>-3.172588864713728</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282102</v>
+        <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.6773952951655</v>
+        <v>-11.51696777669505</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.494324764030684</v>
+        <v>-1.430153756642504</v>
       </c>
       <c r="F1891" t="n">
         <v>-3.172588864713728</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116217</v>
+        <v>3.710931958116216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.73029058320979</v>
+        <v>-11.56986306473934</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.512849105086292</v>
+        <v>-1.448678097698112</v>
       </c>
       <c r="F1892" t="n">
         <v>-3.167633518625282</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081569</v>
+        <v>3.768948099081568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.44638185228104</v>
+        <v>-11.28595433381059</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.393551908476155</v>
+        <v>-1.329380901087975</v>
       </c>
       <c r="F1893" t="n">
         <v>-3.167633518625282</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425328</v>
+        <v>3.728574354425327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.37501545967139</v>
+        <v>-11.21458794120094</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.374742613826162</v>
+        <v>-1.310571606437982</v>
       </c>
       <c r="F1894" t="n">
         <v>-3.096267126015634</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702412</v>
+        <v>3.747699084702411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.11117859246732</v>
+        <v>-10.95075107399687</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.279091348257441</v>
+        <v>-1.214920340869261</v>
       </c>
       <c r="F1895" t="n">
         <v>-3.096267126015634</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906228</v>
+        <v>3.766313503906227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.84393679159892</v>
+        <v>-10.68350927312848</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.174029188409456</v>
+        <v>-1.109858181021277</v>
       </c>
       <c r="F1896" t="n">
         <v>-3.096267126015634</v>
@@ -45182,10 +45182,10 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.74602975292243</v>
+        <v>-10.58560223445198</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.13516668791232</v>
+        <v>-1.070995680524141</v>
       </c>
       <c r="F1897" t="n">
         <v>-3.028281376155078</v>
@@ -45205,10 +45205,10 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.72207621194648</v>
+        <v>-10.56164869347603</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.124916765376443</v>
+        <v>-1.060745757988264</v>
       </c>
       <c r="F1898" t="n">
         <v>-3.00432783517912</v>
@@ -45228,10 +45228,10 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.45801627362368</v>
+        <v>-10.29758875515323</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.032553106209077</v>
+        <v>-0.9683820988208973</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.740267896856324</v>
@@ -45251,10 +45251,10 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.750936650118842</v>
+        <v>-9.590509131648393</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7525082904674432</v>
+        <v>-0.6883372830792633</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.740267896856324</v>
@@ -45274,10 +45274,10 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.710752351752651</v>
+        <v>-9.550324833282202</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7360909472331256</v>
+        <v>-0.6719199398449458</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.700083598490133</v>
@@ -45297,10 +45297,10 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.630682556214847</v>
+        <v>-9.470255037744398</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.7046962077972467</v>
+        <v>-0.6405252004090674</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.620013802952329</v>
@@ -45320,10 +45320,10 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.397201333985247</v>
+        <v>-9.236773815514798</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.6033792900675548</v>
+        <v>-0.5392082826793749</v>
       </c>
       <c r="F1903" t="n">
         <v>-2.386532580722731</v>
@@ -45343,10 +45343,10 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.217492803841374</v>
+        <v>-9.057065285370925</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5343880883229644</v>
+        <v>-0.470217080934785</v>
       </c>
       <c r="F1904" t="n">
         <v>-2.329361076560035</v>
@@ -45366,10 +45366,10 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.085217330210487</v>
+        <v>-8.924789811740037</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4861104121235824</v>
+        <v>-0.421939404735403</v>
       </c>
       <c r="F1905" t="n">
         <v>-2.197085602929148</v>
@@ -45389,10 +45389,10 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.894617655537333</v>
+        <v>-8.734190137066884</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.4070554815666845</v>
+        <v>-0.3428844741785047</v>
       </c>
       <c r="F1906" t="n">
         <v>-2.006485928255995</v>
@@ -45412,10 +45412,10 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.645617856853752</v>
+        <v>-8.485190338383303</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2945492208695932</v>
+        <v>-0.2303782134814134</v>
       </c>
       <c r="F1907" t="n">
         <v>-2.006485928255995</v>
@@ -45435,10 +45435,10 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.751207846626857</v>
+        <v>-8.590780328156407</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4647611463780539</v>
+        <v>-0.4005901389898741</v>
       </c>
       <c r="F1908" t="n">
         <v>-2.1120759180291</v>
@@ -45458,10 +45458,10 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.769942748745454</v>
+        <v>-8.609515230275004</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4237107653484062</v>
+        <v>-0.3595397579602264</v>
       </c>
       <c r="F1909" t="n">
         <v>-2.1120759180291</v>
@@ -45481,10 +45481,10 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.622002707337854</v>
+        <v>-8.461575188867405</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.4844136714735341</v>
+        <v>-0.4202426640853543</v>
       </c>
       <c r="F1910" t="n">
         <v>-2.091755002120542</v>
@@ -45504,10 +45504,10 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.597774070948882</v>
+        <v>-8.437346552478433</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.483436203171423</v>
+        <v>-0.4192651957832436</v>
       </c>
       <c r="F1911" t="n">
         <v>-2.06752636573157</v>
@@ -45527,10 +45527,10 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.55422566417819</v>
+        <v>-8.393798145707741</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.47297745255824</v>
+        <v>-0.4088064451700602</v>
       </c>
       <c r="F1912" t="n">
         <v>-2.06752636573157</v>
@@ -45550,10 +45550,10 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.312077270724332</v>
+        <v>-8.151649752253883</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3616557407955536</v>
+        <v>-0.2974847334073738</v>
       </c>
       <c r="F1913" t="n">
         <v>-2.06752636573157</v>
@@ -45573,10 +45573,10 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.248847898955985</v>
+        <v>-8.088420380485536</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.3418318716290196</v>
+        <v>-0.2776608642408398</v>
       </c>
       <c r="F1914" t="n">
         <v>-2.06752636573157</v>
@@ -45596,10 +45596,10 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.125556764138855</v>
+        <v>-7.965129245668405</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.2950173236915905</v>
+        <v>-0.2308463163034107</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.94423523091444</v>
@@ -45619,10 +45619,10 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-8.104407565235412</v>
+        <v>-7.943980046764962</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.2788566658928886</v>
+        <v>-0.2146856585047079</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.923086032010997</v>
@@ -45642,10 +45642,10 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.860642123251968</v>
+        <v>-7.700214604781517</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.1855697807524601</v>
+        <v>-0.1213987733642798</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.923086032010997</v>
@@ -45665,10 +45665,10 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.596614056058709</v>
+        <v>-7.436186537588258</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.07783423995514038</v>
+        <v>-0.01366323256695967</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.721220633195043</v>
@@ -45688,10 +45688,10 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.346763662109634</v>
+        <v>-7.186336143639183</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.0148479926081917</v>
+        <v>0.07901899999637196</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.721220633195043</v>
@@ -45711,10 +45711,10 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.170871569642202</v>
+        <v>-7.010444051171751</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.08880395311581335</v>
+        <v>0.1529749605039936</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.721220633195043</v>
@@ -45734,10 +45734,10 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.999425106619738</v>
+        <v>-6.838997588149287</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.1707100443793523</v>
+        <v>0.2348810517675326</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.54977417017258</v>
@@ -45757,10 +45757,10 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.774392106950915</v>
+        <v>-6.613964588480465</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.2597437218631784</v>
+        <v>0.3239147292513591</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.324741170503757</v>
@@ -45780,10 +45780,10 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.559757729314509</v>
+        <v>-6.399330210844058</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.3502922739720584</v>
+        <v>0.4144632813602391</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.11010679286735</v>
@@ -45803,10 +45803,10 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.46675768810861</v>
+        <v>-6.30633016963816</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.3686865492382134</v>
+        <v>0.4328575566263937</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.11010679286735</v>
@@ -45826,10 +45826,10 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.22632719130375</v>
+        <v>-6.065899672833299</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.4666018245850352</v>
+        <v>0.5307728319732155</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.8696762960624898</v>
@@ -45849,10 +45849,10 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-6.154084623132555</v>
+        <v>-5.993657104662105</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.4994281656883333</v>
+        <v>0.5635991730765135</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.8696762960624898</v>
@@ -45872,10 +45872,10 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-6.03814477350737</v>
+        <v>-5.877717255036919</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.5464826894557473</v>
+        <v>0.6106536968439276</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.7928545650463659</v>
@@ -45895,10 +45895,10 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.795489185084207</v>
+        <v>-5.635061666613757</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.640542996045006</v>
+        <v>0.7047140034331862</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.7928545650463659</v>
@@ -45918,10 +45918,10 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.575468387047197</v>
+        <v>-5.415040868576746</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.7301303522704243</v>
+        <v>0.7943013596586046</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.6516347199783856</v>
@@ -45941,10 +45941,10 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.376219757142388</v>
+        <v>-5.215792238671937</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.8257239870341713</v>
+        <v>0.8898949944223515</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.6516347199783856</v>
@@ -45964,10 +45964,10 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.216704653623018</v>
+        <v>-5.056277135152567</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.8906758728822211</v>
+        <v>0.9548468802704013</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.4921196164590157</v>
@@ -45987,10 +45987,10 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-5.07203250852328</v>
+        <v>-4.91160499005283</v>
       </c>
       <c r="E1932" t="n">
-        <v>0.9586328334835557</v>
+        <v>1.022803840871736</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.3474474713592783</v>
@@ -46010,10 +46010,10 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-5.131907335880973</v>
+        <v>-4.971479817410522</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9207203939419046</v>
+        <v>0.9848914013300851</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.4073222987169704</v>
@@ -46033,10 +46033,10 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-5.045107838101965</v>
+        <v>-4.884680319631514</v>
       </c>
       <c r="E1934" t="n">
-        <v>0.9778406863760742</v>
+        <v>1.042011693764255</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.4073222987169704</v>
@@ -46056,10 +46056,10 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-5.047577544563771</v>
+        <v>-4.88715002609332</v>
       </c>
       <c r="E1935" t="n">
-        <v>0.9769252051647639</v>
+        <v>1.041096212552944</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.4097920051787766</v>
@@ -46079,10 +46079,10 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-5.115947730887781</v>
+        <v>-4.95552021241733</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.9605840531098617</v>
+        <v>1.024755060498042</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.4005163061425616</v>
@@ -46102,10 +46102,10 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.994531301261304</v>
+        <v>-4.834103782790853</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9995873335923438</v>
+        <v>1.063758340980524</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.4005163061425616</v>
@@ -46125,10 +46125,10 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.02552446059001</v>
+        <v>-4.865096942119559</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8118996349012484</v>
+        <v>0.8760706422894287</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.4005163061425616</v>
@@ -46148,10 +46148,10 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.85005020079754</v>
+        <v>-4.689622682327089</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.886656570810024</v>
+        <v>0.9508275781982043</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.4005163061425616</v>
@@ -46171,10 +46171,10 @@
         <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.960986453438789</v>
+        <v>-4.800558934968338</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8422935436403221</v>
+        <v>0.9064645510285023</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.4005163061425616</v>
@@ -46194,10 +46194,10 @@
         <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.164013030982022</v>
+        <v>-5.003585512511571</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.7642142978429343</v>
+        <v>0.8283853052311145</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.603542883685795</v>
@@ -46217,10 +46217,10 @@
         <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-5.006087432046729</v>
+        <v>-4.845659913576278</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8375569238491838</v>
+        <v>0.9017279312373643</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.603542883685795</v>
@@ -46240,10 +46240,10 @@
         <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-5.154408685857858</v>
+        <v>-4.993981167387407</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.7731746928985928</v>
+        <v>0.837345700286773</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.603542883685795</v>
@@ -46263,10 +46263,10 @@
         <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-5.155591770508918</v>
+        <v>-4.995164252038467</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.764477234482694</v>
+        <v>0.8286482418708743</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.6091859321523065</v>
@@ -46286,10 +46286,10 @@
         <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-5.032464063514835</v>
+        <v>-4.872036545044384</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8142801903134287</v>
+        <v>0.8784511977016092</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.6091859321523065</v>
@@ -46309,10 +46309,10 @@
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.939653582063976</v>
+        <v>-4.779226063593525</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.7806770747851384</v>
+        <v>0.8448480821733186</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.5163754507014472</v>
@@ -46332,10 +46332,10 @@
         <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.891090529842946</v>
+        <v>-4.730663011372495</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.801975771598151</v>
+        <v>0.8661467789863315</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.467812398480417</v>
@@ -46355,10 +46355,10 @@
         <v>2.7538441163608</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.778419311606696</v>
+        <v>-4.617991793136245</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8421199674043742</v>
+        <v>0.9062909747925545</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.3551411802441668</v>
@@ -46378,10 +46378,10 @@
         <v>2.759335412191467</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.666042310424023</v>
+        <v>-4.505614791953572</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.8925620637081106</v>
+        <v>0.9567330710962909</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.3551411802441668</v>
@@ -46401,10 +46401,10 @@
         <v>2.770832613960006</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.864276879310753</v>
+        <v>-4.703849360840302</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8247654379219573</v>
+        <v>0.8889364453101376</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.5533757491308974</v>
@@ -46424,10 +46424,10 @@
         <v>2.609188333960659</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.947278160336032</v>
+        <v>-4.786850641865581</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.629920645512499</v>
+        <v>0.6940916529006793</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.5719466336580712</v>
@@ -46447,10 +46447,10 @@
         <v>2.729337994679865</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.788083888279456</v>
+        <v>-4.627656369809005</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8137480150543352</v>
+        <v>0.8779190224425157</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.5719466336580712</v>
@@ -46470,10 +46470,10 @@
         <v>2.743851020782188</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.874682471260559</v>
+        <v>-4.714254952790108</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7936216079642171</v>
+        <v>0.8577926153523974</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.5719466336580712</v>
@@ -46493,10 +46493,10 @@
         <v>2.741270462124556</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.836298808702407</v>
+        <v>-4.675871290231957</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8063945143298463</v>
+        <v>0.8705655217180266</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.53356297109992</v>
@@ -46516,10 +46516,10 @@
         <v>2.737999490969859</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.659182478667241</v>
+        <v>-4.49875496019679</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.873970075189215</v>
+        <v>0.9381410825773955</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.53356297109992</v>
@@ -46539,10 +46539,10 @@
         <v>2.738682882731772</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.629480354690948</v>
+        <v>-4.469052836220497</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8865343165416455</v>
+        <v>0.950705323929826</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.5380330963152333</v>
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.422844493121749</v>
+        <v>3.821556057887443</v>
       </c>
       <c r="C1957" t="n">
         <v>2.732469858038186</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.445165103927396</v>
+        <v>-4.443003676544823</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9540473921534807</v>
+        <v>0.9549119631065099</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.377249532527361</v>
+        <v>-0.4399470936417478</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.50612013852177</v>
+        <v>2.468501601853138</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240508.xlsx
+++ b/tame_output/ON/bt/strategyON_20240508.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.5%</t>
+          <t>-79.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>113.8%</t>
+          <t>114.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.8%</t>
+          <t>92.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.0%</t>
+          <t>-75.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>94.5%</t>
+          <t>94.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.2%</t>
+          <t>-9.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-605.9%</t>
+          <t>-590.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.9%</t>
+          <t>-1.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-280.7%</t>
+          <t>-274.6%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-30.3%</t>
+          <t>-29.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>69.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-24.6%</t>
+          <t>-23.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-156.7%</t>
+          <t>-157.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-268.0%</t>
+          <t>-262.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-199.2%</t>
+          <t>-195.7%</t>
         </is>
       </c>
     </row>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094118</v>
+        <v>3.374439043094119</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199288</v>
+        <v>3.405960511199289</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309728</v>
+        <v>3.833249172309727</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858731</v>
+        <v>3.83937087185873</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096477</v>
+        <v>3.856158176096476</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349969</v>
+        <v>3.82232342234997</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972342</v>
+        <v>3.848613050972343</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.76502074769545</v>
+        <v>3.765020747695449</v>
       </c>
       <c r="C1940" t="n">
         <v>2.827044549329585</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581296</v>
+        <v>3.773206721581294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.83017593454949</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734165</v>
+        <v>3.784340376734163</v>
       </c>
       <c r="C1942" t="n">
         <v>2.840348320981623</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212301</v>
+        <v>3.7869463822123</v>
       </c>
       <c r="C1943" t="n">
         <v>2.835294591555483</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786049</v>
+        <v>3.752023923786047</v>
       </c>
       <c r="C1944" t="n">
         <v>2.827070367000009</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273194</v>
+        <v>3.753567590273192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.82762224003311</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279503</v>
+        <v>3.733387025279502</v>
       </c>
       <c r="C1946" t="n">
         <v>2.756894931924476</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030431</v>
+        <v>3.748282241030429</v>
       </c>
       <c r="C1947" t="n">
         <v>2.758768407849077</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942743</v>
+        <v>3.721073619942741</v>
       </c>
       <c r="C1948" t="n">
         <v>2.7538441163608</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268541</v>
+        <v>3.743044028268539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.759335412191467</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968866</v>
+        <v>3.689594264968865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.770832613960006</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175327</v>
+        <v>3.643066046175325</v>
       </c>
       <c r="C1951" t="n">
         <v>2.609188333960659</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199273</v>
+        <v>3.682712735199272</v>
       </c>
       <c r="C1952" t="n">
         <v>2.729337994679865</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660773</v>
+        <v>3.733008865660771</v>
       </c>
       <c r="C1953" t="n">
         <v>2.743851020782188</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383429</v>
+        <v>3.741170494383427</v>
       </c>
       <c r="C1954" t="n">
         <v>2.741270462124556</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002489</v>
+        <v>3.751143622002488</v>
       </c>
       <c r="C1955" t="n">
         <v>2.737999490969859</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263907</v>
+        <v>3.741324873263905</v>
       </c>
       <c r="C1956" t="n">
         <v>2.738682882731772</v>
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.821556057887443</v>
+        <v>3.821556057887442</v>
       </c>
       <c r="C1957" t="n">
         <v>2.732469858038186</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.443003676544823</v>
+        <v>-4.289677414981729</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9549119631065099</v>
+        <v>1.016242467731747</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.4399470936417478</v>
+        <v>-0.3812563381445147</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.468501601853138</v>
+        <v>2.503716055151478</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240508.xlsx
+++ b/tame_output/ON/bt/strategyON_20240508.xlsx
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097823</v>
+        <v>3.341378723097822</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094119</v>
+        <v>3.374439043094118</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199289</v>
+        <v>3.405960511199288</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737173</v>
+        <v>3.503515506737172</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611698</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199888</v>
+        <v>3.496848329199889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910631</v>
+        <v>3.499968163910632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587501888027</v>
+        <v>3.485875018880271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234396</v>
+        <v>3.480688917234397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860585</v>
+        <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792542</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003468962892</v>
+        <v>3.600034689628921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691568158410718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68515780608528</v>
+        <v>3.685157806085281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282101</v>
+        <v>3.684840248282102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116216</v>
+        <v>3.710931958116217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081568</v>
+        <v>3.768948099081569</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425327</v>
+        <v>3.728574354425328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702411</v>
+        <v>3.747699084702412</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906227</v>
+        <v>3.766313503906228</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096476</v>
+        <v>3.856158176096475</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837688</v>
+        <v>3.821589933837687</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.82232342234997</v>
+        <v>3.822323422349969</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972343</v>
+        <v>3.848613050972342</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145942</v>
+        <v>3.818665376145941</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009954</v>
+        <v>3.843270952009953</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675905</v>
+        <v>3.746038950675904</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695449</v>
+        <v>3.765020747695448</v>
       </c>
       <c r="C1940" t="n">
         <v>2.827044549329585</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.821556057887442</v>
+        <v>3.821556057887441</v>
       </c>
       <c r="C1957" t="n">
         <v>2.732469858038186</v>

--- a/tame_output/ON/bt/strategyON_20240508.xlsx
+++ b/tame_output/ON/bt/strategyON_20240508.xlsx
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1954</v>
+        <v>1955</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1954</v>
+        <v>1955</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -829,17 +829,17 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-38.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1954</v>
+        <v>1955</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.4%</t>
+          <t>-75.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>94.8%</t>
+          <t>94.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1954</v>
+        <v>1955</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-29.7%</t>
+          <t>-29.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1954</v>
+        <v>1955</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-23.9%</t>
+          <t>-23.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1954</v>
+        <v>1955</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-195.7%</t>
+          <t>-154.9%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1957"/>
+  <dimension ref="A1:G1958"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341316</v>
+        <v>3.503170282341315</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776679</v>
+        <v>3.500446096776678</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611698</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199889</v>
+        <v>3.496848329199888</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910632</v>
+        <v>3.499968163910631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.48587501888027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234397</v>
+        <v>3.480688917234396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.493712438860585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.60003468962892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410718</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085281</v>
+        <v>3.68515780608528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282102</v>
+        <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116217</v>
+        <v>3.710931958116216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081569</v>
+        <v>3.768948099081568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425328</v>
+        <v>3.728574354425327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702412</v>
+        <v>3.747699084702411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906228</v>
+        <v>3.766313503906227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487774</v>
+        <v>3.789307536487773</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309727</v>
+        <v>3.833249172309726</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.83937087185873</v>
+        <v>3.839370871858729</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096475</v>
+        <v>3.856158176096474</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78732685376181</v>
+        <v>3.787326853761809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255787</v>
+        <v>3.801633547255786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860429</v>
+        <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575955</v>
+        <v>3.784715218575953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430989</v>
+        <v>3.753878996430987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077645</v>
+        <v>3.692928280077643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457903</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180811</v>
+        <v>3.760330111180809</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879204</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568109</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.78291895796342</v>
+        <v>3.782918957963418</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192818</v>
+        <v>3.828547911192817</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262049</v>
+        <v>3.828049353262047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389911</v>
+        <v>3.812450103389909</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788096</v>
+        <v>3.748324832788094</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527527</v>
+        <v>3.824307657527525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749186</v>
+        <v>3.826351398749184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481499</v>
+        <v>3.835954411481497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862989</v>
+        <v>3.780930335862987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102783</v>
+        <v>3.773761647102782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353076</v>
+        <v>3.764614304353074</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544785</v>
+        <v>3.798811195544783</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712296</v>
+        <v>3.797691308712294</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837687</v>
+        <v>3.821589933837685</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349969</v>
+        <v>3.822323422349967</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972342</v>
+        <v>3.84861305097234</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145941</v>
+        <v>3.818665376145939</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009953</v>
+        <v>3.843270952009951</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966262</v>
+        <v>3.84504381096626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046999</v>
+        <v>3.791269976046997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412106</v>
+        <v>3.735835647412104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144519</v>
+        <v>3.762643902144517</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900696</v>
+        <v>3.729142822900695</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473603</v>
+        <v>3.743216620473602</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978372</v>
+        <v>3.714175563978371</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887706</v>
+        <v>3.710903155887705</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675904</v>
+        <v>3.746038950675902</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695448</v>
+        <v>3.765020747695447</v>
       </c>
       <c r="C1940" t="n">
         <v>2.827044549329585</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581294</v>
+        <v>3.773206721581293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.83017593454949</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734163</v>
+        <v>3.784340376734161</v>
       </c>
       <c r="C1942" t="n">
         <v>2.840348320981623</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869463822123</v>
+        <v>3.786946382212298</v>
       </c>
       <c r="C1943" t="n">
         <v>2.835294591555483</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786047</v>
+        <v>3.752023923786045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.827070367000009</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273192</v>
+        <v>3.753567590273191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.82762224003311</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279502</v>
+        <v>3.7333870252795</v>
       </c>
       <c r="C1946" t="n">
         <v>2.756894931924476</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030429</v>
+        <v>3.748282241030427</v>
       </c>
       <c r="C1947" t="n">
         <v>2.758768407849077</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942741</v>
+        <v>3.721073619942739</v>
       </c>
       <c r="C1948" t="n">
         <v>2.7538441163608</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268539</v>
+        <v>3.743044028268537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.759335412191467</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968865</v>
+        <v>3.689594264968863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.770832613960006</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175325</v>
+        <v>3.643066046175323</v>
       </c>
       <c r="C1951" t="n">
         <v>2.609188333960659</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199272</v>
+        <v>3.68271273519927</v>
       </c>
       <c r="C1952" t="n">
         <v>2.729337994679865</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660771</v>
+        <v>3.73300886566077</v>
       </c>
       <c r="C1953" t="n">
         <v>2.743851020782188</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383427</v>
+        <v>3.741170494383425</v>
       </c>
       <c r="C1954" t="n">
         <v>2.741270462124556</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002488</v>
+        <v>3.751143622002486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.737999490969859</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263905</v>
+        <v>3.741324873263904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.738682882731772</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.821556057887441</v>
+        <v>3.735861515710477</v>
       </c>
       <c r="C1957" t="n">
         <v>2.732469858038186</v>
@@ -46572,6 +46572,29 @@
       </c>
       <c r="G1957" t="n">
         <v>2.503716055151478</v>
+      </c>
+    </row>
+    <row r="1958">
+      <c r="A1958" s="2" t="n">
+        <v>45420</v>
+      </c>
+      <c r="B1958" t="n">
+        <v>3.822026809697184</v>
+      </c>
+      <c r="C1958" t="n">
+        <v>2.917745580487016</v>
+      </c>
+      <c r="D1958" t="n">
+        <v>-4.289677414981729</v>
+      </c>
+      <c r="E1958" t="n">
+        <v>1.016242467731747</v>
+      </c>
+      <c r="F1958" t="n">
+        <v>-0.3812563381445147</v>
+      </c>
+      <c r="G1958" t="n">
+        <v>2.910809377473384</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240508.xlsx
+++ b/tame_output/ON/bt/strategyON_20240508.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>55.1%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>61.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-27.3%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.0%</t>
+          <t>-79.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>114.1%</t>
+          <t>113.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>134.1%</t>
+          <t>134.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.4%</t>
+          <t>91.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-56.3%</t>
+          <t>-56.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.3%</t>
+          <t>-76.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>94.7%</t>
+          <t>94.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.2%</t>
+          <t>444.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.4%</t>
+          <t>-9.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-590.5%</t>
+          <t>-606.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-44.0%</t>
+          <t>-44.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-2.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-52.4%</t>
+          <t>-77.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-274.6%</t>
+          <t>-281.1%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-29.6%</t>
+          <t>-31.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-23.6%</t>
+          <t>-25.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-157.5%</t>
+          <t>-158.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-262.1%</t>
+          <t>-276.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-16.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-154.9%</t>
+          <t>-162.4%</t>
         </is>
       </c>
     </row>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097822</v>
+        <v>3.341378723097823</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.838602165915842</v>
+        <v>-7.999029684386291</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.01691859698739551</v>
+        <v>-0.08108960437557489</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.741209520764524</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.18447698790065</v>
+        <v>-8.206837707120693</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1591689606356237</v>
+        <v>-0.1681132483236407</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.741209520764524</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.346619258363743</v>
+        <v>-8.368979977583786</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2256209487658598</v>
+        <v>-0.2345652364538768</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.741209520764524</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.643280600173942</v>
+        <v>-8.665641319393984</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3405065095607309</v>
+        <v>-0.3494507972487479</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.809952656498403</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.076629708284177</v>
+        <v>-9.098990427504219</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.5178724573392284</v>
+        <v>-0.5268167450272454</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.809952656498403</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.459631097026808</v>
+        <v>-9.48199181624685</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.6711751141578648</v>
+        <v>-0.6801194018458818</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.809952656498403</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.617029977239929</v>
+        <v>-9.639390696459971</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.7315631502716831</v>
+        <v>-0.7405074379597001</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.967351536711524</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.97656029974393</v>
+        <v>-9.998921018963973</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.8700249759752334</v>
+        <v>-0.8789692636632505</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.967351536711524</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341315</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.30296032840894</v>
+        <v>-10.32532104762899</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.9926689674840614</v>
+        <v>-1.001613255172078</v>
       </c>
       <c r="F1875" t="n">
         <v>-2.293751565376537</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776678</v>
+        <v>3.500446096776679</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.52210929648314</v>
+        <v>-10.54447001570318</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.077286804091971</v>
+        <v>-1.086231091779988</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.512900533450734</v>
@@ -44722,10 +44722,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.51841837152673</v>
+        <v>-10.54077909074677</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.075810434109407</v>
+        <v>-1.084754721797424</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.512900533450734</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611698</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.72267654685659</v>
+        <v>-10.74503726607664</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.15200050712271</v>
+        <v>-1.160944794810727</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.640539478064723</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199888</v>
+        <v>3.496848329199889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.94071431848777</v>
+        <v>-10.96307503770781</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.234733061290745</v>
+        <v>-1.243677348978762</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.815310246160622</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910631</v>
+        <v>3.499968163910632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.86724448682032</v>
+        <v>-10.88960520604036</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.189973427130345</v>
+        <v>-1.198917714818362</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.741840414493173</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.04236890420687</v>
+        <v>-11.06472962342691</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.245467973337445</v>
+        <v>-1.254412261025462</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.916964831879717</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587501888027</v>
+        <v>3.485875018880271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.27682099822136</v>
+        <v>-11.2991817174414</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.346467975844837</v>
+        <v>-1.355412263532854</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.916964831879717</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234396</v>
+        <v>3.480688917234397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.56462484275859</v>
+        <v>-11.58698556197864</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.468261704433708</v>
+        <v>-1.477205992121725</v>
       </c>
       <c r="F1883" t="n">
         <v>-3.204768676416955</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860585</v>
+        <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.79444928992242</v>
+        <v>-11.81681000914246</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.559075693460682</v>
+        <v>-1.568019981148699</v>
       </c>
       <c r="F1884" t="n">
         <v>-3.367416213487116</v>
@@ -44906,10 +44906,10 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.02647820965868</v>
+        <v>-12.04883892887872</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.649193532726072</v>
+        <v>-1.658137820414089</v>
       </c>
       <c r="F1885" t="n">
         <v>-3.429428910675539</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792542</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.97446269568987</v>
+        <v>-11.99682341490991</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.624396991452146</v>
+        <v>-1.633341279140163</v>
       </c>
       <c r="F1886" t="n">
         <v>-3.429428910675539</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003468962892</v>
+        <v>3.600034689628921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.11613453741399</v>
+        <v>-12.13849525663403</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.682540955040536</v>
+        <v>-1.691485242728553</v>
       </c>
       <c r="F1887" t="n">
         <v>-3.429428910675539</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691568158410718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.06654369298915</v>
+        <v>-12.0889044122092</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.64765120710573</v>
+        <v>-1.656595494793747</v>
       </c>
       <c r="F1888" t="n">
         <v>-3.379838066250705</v>
@@ -44998,10 +44998,10 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.86739158575205</v>
+        <v>-11.8897523049721</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.581041497857573</v>
+        <v>-1.58998578554559</v>
       </c>
       <c r="F1889" t="n">
         <v>-3.214515540300892</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68515780608528</v>
+        <v>3.685157806085281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.64154643303264</v>
+        <v>-11.66390715225269</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.4811243637336</v>
+        <v>-1.490068651421617</v>
       </c>
       <c r="F1890" t="n">
         <v>-3.172588864713728</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282101</v>
+        <v>3.684840248282102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.51696777669505</v>
+        <v>-11.5393284959151</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.430153756642504</v>
+        <v>-1.439098044330521</v>
       </c>
       <c r="F1891" t="n">
         <v>-3.172588864713728</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116216</v>
+        <v>3.710931958116217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.56986306473934</v>
+        <v>-11.59222378395938</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.448678097698112</v>
+        <v>-1.457622385386129</v>
       </c>
       <c r="F1892" t="n">
         <v>-3.167633518625282</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081568</v>
+        <v>3.768948099081569</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.28595433381059</v>
+        <v>-11.30831505303063</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.329380901087975</v>
+        <v>-1.338325188775992</v>
       </c>
       <c r="F1893" t="n">
         <v>-3.167633518625282</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425327</v>
+        <v>3.728574354425328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.21458794120094</v>
+        <v>-11.23694866042099</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.310571606437982</v>
+        <v>-1.319515894125999</v>
       </c>
       <c r="F1894" t="n">
         <v>-3.096267126015634</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702411</v>
+        <v>3.747699084702412</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.95075107399687</v>
+        <v>-10.97311179321692</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.214920340869261</v>
+        <v>-1.223864628557279</v>
       </c>
       <c r="F1895" t="n">
         <v>-3.096267126015634</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906227</v>
+        <v>3.766313503906228</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.68350927312848</v>
+        <v>-10.70586999234852</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.109858181021277</v>
+        <v>-1.118802468709294</v>
       </c>
       <c r="F1896" t="n">
         <v>-3.096267126015634</v>
@@ -45182,10 +45182,10 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.58560223445198</v>
+        <v>-10.60796295367203</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.070995680524141</v>
+        <v>-1.079939968212158</v>
       </c>
       <c r="F1897" t="n">
         <v>-3.028281376155078</v>
@@ -45205,10 +45205,10 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.56164869347603</v>
+        <v>-10.58400941269607</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.060745757988264</v>
+        <v>-1.069690045676281</v>
       </c>
       <c r="F1898" t="n">
         <v>-3.00432783517912</v>
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.29758875515323</v>
+        <v>-10.46027778434714</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.9683820988208973</v>
+        <v>-1.03345771049846</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.740267896856324</v>
+        <v>-2.880596206830189</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.506849089440348</v>
+        <v>1.422652103456029</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.590509131648393</v>
+        <v>-9.753198160842301</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.6883372830792633</v>
+        <v>-0.7534128947568268</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.740267896856324</v>
+        <v>-2.880596206830189</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.504062055780047</v>
+        <v>1.419865069795728</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.550324833282202</v>
+        <v>-9.71301386247611</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.6719199398449458</v>
+        <v>-0.7369955515225093</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.700083598490133</v>
+        <v>-2.840411908463998</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.528516258687603</v>
+        <v>1.444319272703284</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096474</v>
+        <v>3.856158176096475</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.470255037744398</v>
+        <v>-9.632944066938306</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6405252004090674</v>
+        <v>-0.7056008120866304</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.620013802952329</v>
+        <v>-2.760342112926194</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.575924957231042</v>
+        <v>1.491727971246723</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761809</v>
+        <v>3.78732685376181</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.236773815514798</v>
+        <v>-9.399462844708708</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.5392082826793749</v>
+        <v>-0.6042838943569389</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.386532580722731</v>
+        <v>-2.526860890696595</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.723938119406654</v>
+        <v>1.639741133422335</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255786</v>
+        <v>3.801633547255787</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.057065285370925</v>
+        <v>-9.219754314564835</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.470217080934785</v>
+        <v>-0.5352926926123489</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.329361076560035</v>
+        <v>-2.469689386533899</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.755348811591312</v>
+        <v>1.671151825606993</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.763178672860429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.924789811740037</v>
+        <v>-9.087478840933947</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.421939404735403</v>
+        <v>-0.487015016412967</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.197085602929148</v>
+        <v>-2.337413912903013</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.830081582516871</v>
+        <v>1.745884596532552</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575953</v>
+        <v>3.784715218575955</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.734190137066884</v>
+        <v>-8.896879166260794</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.3428844741785047</v>
+        <v>-0.4079600858560686</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.006485928255995</v>
+        <v>-2.14681423822986</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.947256448008399</v>
+        <v>1.86305946202408</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430987</v>
+        <v>3.753878996430989</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.485190338383303</v>
+        <v>-8.647879367577213</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2303782134814134</v>
+        <v>-0.2954538251589773</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.006485928255995</v>
+        <v>-2.14681423822986</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.960162789232058</v>
+        <v>1.875965803247739</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077643</v>
+        <v>3.692928280077645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.590780328156407</v>
+        <v>-8.753469357350317</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4005901389898741</v>
+        <v>-0.465665750667438</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.1120759180291</v>
+        <v>-2.252404228002965</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.768832865768977</v>
+        <v>1.684635879784658</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.770419008457903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.609515230275004</v>
+        <v>-8.772204259468914</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3595397579602264</v>
+        <v>-0.4246153696377903</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.1120759180291</v>
+        <v>-2.252404228002965</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.817377207646063</v>
+        <v>1.733180221661744</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180809</v>
+        <v>3.760330111180811</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.461575188867405</v>
+        <v>-8.624264218061315</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.4202426640853543</v>
+        <v>-0.4853182757629182</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.091755002120542</v>
+        <v>-2.232083312094407</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.70969083450303</v>
+        <v>1.625493848518711</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.437346552478433</v>
+        <v>-8.600035581672342</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4192651957832436</v>
+        <v>-0.4843408074608075</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.06752636573157</v>
+        <v>-2.207854675705435</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.715514030082935</v>
+        <v>1.631317044098616</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568109</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.393798145707741</v>
+        <v>-8.556487174901651</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.4088064451700602</v>
+        <v>-0.4738820568476241</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.06752636573157</v>
+        <v>-2.207854675705435</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.708553417987842</v>
+        <v>1.624356432003523</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963418</v>
+        <v>3.78291895796342</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.151649752253883</v>
+        <v>-8.314338781447793</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.2974847334073738</v>
+        <v>-0.3625603450849377</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.06752636573157</v>
+        <v>-2.207854675705435</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.723015772368985</v>
+        <v>1.638818786384666</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192817</v>
+        <v>3.828547911192818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.088420380485536</v>
+        <v>-8.251109409679446</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.2776608642408398</v>
+        <v>-0.3427364759184037</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.06752636573157</v>
+        <v>-2.207854675705435</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.71754789282818</v>
+        <v>1.633350906843861</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.828049353262049</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.965129245668405</v>
+        <v>-8.127818274862316</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.2308463163034107</v>
+        <v>-0.2959219279809751</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.94423523091444</v>
+        <v>-2.084563540888305</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.789020667729035</v>
+        <v>1.704823681744716</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389909</v>
+        <v>3.812450103389911</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.943980046764962</v>
+        <v>-8.106669075958873</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.2146856585047079</v>
+        <v>-0.2797612701822727</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.923086032010997</v>
+        <v>-2.063414341984861</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.809411165308426</v>
+        <v>1.725214179324108</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788094</v>
+        <v>3.748324832788096</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.700214604781517</v>
+        <v>-7.862903633975429</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.1213987733642798</v>
+        <v>-0.1864743850418442</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.923086032010997</v>
+        <v>-2.063414341984861</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.805191873655477</v>
+        <v>1.720994887671158</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527525</v>
+        <v>3.824307657527527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.436186537588258</v>
+        <v>-7.598875566782169</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.01366323256695967</v>
+        <v>-0.07873884424452449</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.721220633195043</v>
+        <v>-1.861548943168908</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.928435426865065</v>
+        <v>1.844238440880746</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749184</v>
+        <v>3.826351398749186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.186336143639183</v>
+        <v>-7.349025172833095</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.07901899999637196</v>
+        <v>0.01394338831880759</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.721220633195043</v>
+        <v>-1.861548943168908</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.921177501848767</v>
+        <v>1.836980515864449</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481497</v>
+        <v>3.835954411481499</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.010444051171751</v>
+        <v>-7.173133080365663</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.1529749605039936</v>
+        <v>0.08789934882642925</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.721220633195043</v>
+        <v>-1.861548943168908</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.924776625369416</v>
+        <v>1.840579639385097</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862987</v>
+        <v>3.780930335862989</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.838997588149287</v>
+        <v>-7.001686617343199</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.2348810517675326</v>
+        <v>0.1698054400899682</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.54977417017258</v>
+        <v>-1.690102480146444</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.040972009237448</v>
+        <v>1.956775023253129</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102782</v>
+        <v>3.773761647102783</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.613964588480465</v>
+        <v>-6.776653617674376</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.3239147292513591</v>
+        <v>0.2588391175737943</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.324741170503757</v>
+        <v>-1.465069480477621</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.175012286655038</v>
+        <v>2.09081530067072</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353074</v>
+        <v>3.764614304353076</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.399330210844058</v>
+        <v>-6.562019240037969</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4144632813602391</v>
+        <v>0.3493876696826743</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.11010679286735</v>
+        <v>-1.250435102841215</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.3084877142912</v>
+        <v>2.224290728306881</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544783</v>
+        <v>3.798811195544785</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.30633016963816</v>
+        <v>-6.469019198832071</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4328575566263937</v>
+        <v>0.3677819449488293</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.11010679286735</v>
+        <v>-1.250435102841215</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.289681973074996</v>
+        <v>2.205484987090677</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712294</v>
+        <v>3.797691308712296</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.065899672833299</v>
+        <v>-6.228588702027211</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.5307728319732155</v>
+        <v>0.4656972202956506</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.8696762960624898</v>
+        <v>-1.010004606036354</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.435683347782789</v>
+        <v>2.35148636179847</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837685</v>
+        <v>3.821589933837687</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.993657104662105</v>
+        <v>-6.156346133856016</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.5635991730765135</v>
+        <v>0.4985235613989487</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.8696762960624898</v>
+        <v>-1.010004606036354</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.439612661617609</v>
+        <v>2.35541567563329</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349967</v>
+        <v>3.822323422349969</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.877717255036919</v>
+        <v>-6.040406284230831</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6106536968439276</v>
+        <v>0.5455780851663627</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.7928545650463659</v>
+        <v>-0.9331828750202305</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.486384284144624</v>
+        <v>2.402187298160305</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.84861305097234</v>
+        <v>3.848613050972342</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.635061666613757</v>
+        <v>-5.797750695807668</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7047140034331862</v>
+        <v>0.6396383917556214</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.7928545650463659</v>
+        <v>-0.9331828750202305</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.483382355364617</v>
+        <v>2.399185369380298</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145939</v>
+        <v>3.818665376145941</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.415040868576746</v>
+        <v>-5.577729897770658</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.7943013596586046</v>
+        <v>0.7292257479810398</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.6516347199783856</v>
+        <v>-0.7919630299522502</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.569693299416019</v>
+        <v>2.485496313431701</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009951</v>
+        <v>3.843270952009953</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.215792238671937</v>
+        <v>-5.378481267865848</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.8898949944223515</v>
+        <v>0.8248193827447867</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.6516347199783856</v>
+        <v>-0.7919630299522502</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.585587482217842</v>
+        <v>2.501390496233524</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504381096626</v>
+        <v>3.845043810966262</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.056277135152567</v>
+        <v>-5.218966164346479</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9548468802704013</v>
+        <v>0.8897712685928365</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4921196164590157</v>
+        <v>-0.6324479264328803</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.682442388769766</v>
+        <v>2.598245402785448</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046997</v>
+        <v>3.791269976046999</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.91160499005283</v>
+        <v>-5.074294019246741</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.022803840871736</v>
+        <v>0.9577282291941716</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3474474713592783</v>
+        <v>-0.4877757813331429</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.779333778391049</v>
+        <v>2.69513679240673</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412104</v>
+        <v>3.735835647412106</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.971479817410522</v>
+        <v>-5.134168846604434</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9848914013300851</v>
+        <v>0.9198157896525205</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.4073222987169704</v>
+        <v>-0.547650608690835</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.729446373377859</v>
+        <v>2.645249387393541</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144517</v>
+        <v>3.762643902144519</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.884680319631514</v>
+        <v>-5.047369348825425</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.042011693764255</v>
+        <v>0.9769360820866897</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.4073222987169704</v>
+        <v>-0.547650608690835</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.751846866700425</v>
+        <v>2.667649880716107</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900695</v>
+        <v>3.729142822900696</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.88715002609332</v>
+        <v>-5.049839055287231</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.041096212552944</v>
+        <v>0.9760206008753798</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.4097920051787766</v>
+        <v>-0.5501203151526413</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.750437444196754</v>
+        <v>2.666240458212435</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473602</v>
+        <v>3.743216620473603</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.95552021241733</v>
+        <v>-5.118209241611241</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.024755060498042</v>
+        <v>0.9596794488204776</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.4005163061425616</v>
+        <v>-0.5408446161164263</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.767009786093185</v>
+        <v>2.682812800108866</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978371</v>
+        <v>3.714175563978372</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.834103782790853</v>
+        <v>-4.996792811984765</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.063758340980524</v>
+        <v>0.9986827293029594</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.4005163061425616</v>
+        <v>-0.5408446161164263</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.757446494725076</v>
+        <v>2.673249508740757</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887705</v>
+        <v>3.710903155887706</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.865096942119559</v>
+        <v>-5.02778597131347</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8760706422894287</v>
+        <v>0.8109950306118643</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.4005163061425616</v>
+        <v>-0.5408446161164263</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.582156059765463</v>
+        <v>2.497959073781144</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675902</v>
+        <v>3.746038950675904</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.689622682327089</v>
+        <v>-4.852311711521001</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9508275781982043</v>
+        <v>0.8857519665206397</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.4005163061425616</v>
+        <v>-0.5408446161164263</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.58672329175725</v>
+        <v>2.502526305772932</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695447</v>
+        <v>3.765020747695448</v>
       </c>
       <c r="C1940" t="n">
         <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.800558934968338</v>
+        <v>-4.96324796416225</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9064645510285023</v>
+        <v>0.8413889393509377</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.4005163061425616</v>
+        <v>-0.5408446161164263</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.586734765644048</v>
+        <v>2.502537779659729</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581293</v>
+        <v>3.773206721581294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.003585512511571</v>
+        <v>-5.166274541705483</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8283853052311145</v>
+        <v>0.7633096935535502</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.603542883685795</v>
+        <v>-0.7438711936596597</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.468050204338013</v>
+        <v>2.383853218353695</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734161</v>
+        <v>3.784340376734163</v>
       </c>
       <c r="C1942" t="n">
         <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.845659913576278</v>
+        <v>-5.00834894277019</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9017279312373643</v>
+        <v>0.8366523195597995</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.603542883685795</v>
+        <v>-0.7438711936596597</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.478222590770146</v>
+        <v>2.394025604785827</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212298</v>
+        <v>3.7869463822123</v>
       </c>
       <c r="C1943" t="n">
         <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.993981167387407</v>
+        <v>-5.156670196581318</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.837345700286773</v>
+        <v>0.7722700886092082</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.603542883685795</v>
+        <v>-0.7438711936596597</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.473168861344006</v>
+        <v>2.388971875359688</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786045</v>
+        <v>3.752023923786047</v>
       </c>
       <c r="C1944" t="n">
         <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.995164252038467</v>
+        <v>-5.157853281232379</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8286482418708743</v>
+        <v>0.7635726301933099</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.6091859321523065</v>
+        <v>-0.7495142421261712</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.461558807708625</v>
+        <v>2.377361821724306</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273191</v>
+        <v>3.753567590273192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.872036545044384</v>
+        <v>-5.034725574238296</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8784511977016092</v>
+        <v>0.8133755860240446</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.6091859321523065</v>
+        <v>-0.7495142421261712</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.462110680741727</v>
+        <v>2.377913694757408</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333870252795</v>
+        <v>3.733387025279502</v>
       </c>
       <c r="C1946" t="n">
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.779226063593525</v>
+        <v>-4.941915092787436</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8448480821733186</v>
+        <v>0.779772470495754</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.5163754507014472</v>
+        <v>-0.6567037606753119</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.447069661503608</v>
+        <v>2.362872675519289</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030427</v>
+        <v>3.748282241030429</v>
       </c>
       <c r="C1947" t="n">
         <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.730663011372495</v>
+        <v>-4.893352040566406</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8661467789863315</v>
+        <v>0.8010711673087667</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.467812398480417</v>
+        <v>-0.6081407084542817</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.478080968760827</v>
+        <v>2.393883982776508</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942739</v>
+        <v>3.721073619942741</v>
       </c>
       <c r="C1948" t="n">
         <v>2.7538441163608</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.617991793136245</v>
+        <v>-4.780680822330156</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9062909747925545</v>
+        <v>0.8412153631149899</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.3551411802441668</v>
+        <v>-0.4954694902180315</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.5407594082143</v>
+        <v>2.456562422229981</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268537</v>
+        <v>3.743044028268539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.759335412191467</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.505614791953572</v>
+        <v>-4.668303821147483</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9567330710962909</v>
+        <v>0.8916574594187263</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.3551411802441668</v>
+        <v>-0.4954694902180315</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.546250704044967</v>
+        <v>2.462053718060648</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968863</v>
+        <v>3.689594264968865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.770832613960006</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.703849360840302</v>
+        <v>-4.866538390034214</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8889364453101376</v>
+        <v>0.823860833632573</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.5533757491308974</v>
+        <v>-0.6937040591047621</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.438807164481468</v>
+        <v>2.354610178497149</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175323</v>
+        <v>3.643066046175325</v>
       </c>
       <c r="C1951" t="n">
         <v>2.609188333960659</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.786850641865581</v>
+        <v>-4.949539671059493</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6940916529006793</v>
+        <v>0.6290160412231147</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.5719466336580712</v>
+        <v>-0.7122749436319358</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.266020353765817</v>
+        <v>2.181823367781498</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.68271273519927</v>
+        <v>3.682712735199272</v>
       </c>
       <c r="C1952" t="n">
         <v>2.729337994679865</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.627656369809005</v>
+        <v>-4.790345399002916</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8779190224425157</v>
+        <v>0.8128434107649509</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.5719466336580712</v>
+        <v>-0.7122749436319358</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.386170014485022</v>
+        <v>2.301973028500703</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.73300886566077</v>
+        <v>3.733008865660771</v>
       </c>
       <c r="C1953" t="n">
         <v>2.743851020782188</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.714254952790108</v>
+        <v>-4.876943981984019</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8577926153523974</v>
+        <v>0.7927170036748328</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.5719466336580712</v>
+        <v>-0.7122749436319358</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.400683040587345</v>
+        <v>2.316486054603026</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383425</v>
+        <v>3.741170494383427</v>
       </c>
       <c r="C1954" t="n">
         <v>2.741270462124556</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.675871290231957</v>
+        <v>-4.838560319425868</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8705655217180266</v>
+        <v>0.805489910040462</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.53356297109992</v>
+        <v>-0.6738912810737846</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.421132679464605</v>
+        <v>2.336935693480286</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002486</v>
+        <v>3.751143622002488</v>
       </c>
       <c r="C1955" t="n">
         <v>2.737999490969859</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.49875496019679</v>
+        <v>-4.661443989390702</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9381410825773955</v>
+        <v>0.8730654708998307</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.53356297109992</v>
+        <v>-0.6738912810737846</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.417861708309907</v>
+        <v>2.333664722325588</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263904</v>
+        <v>3.741324873263905</v>
       </c>
       <c r="C1956" t="n">
         <v>2.738682882731772</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.469052836220497</v>
+        <v>-4.631741865414408</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.950705323929826</v>
+        <v>0.8856297122522614</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.5380330963152333</v>
+        <v>-0.6783614062890979</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.415863024942632</v>
+        <v>2.331666038958313</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.735861515710477</v>
+        <v>3.735861515710479</v>
       </c>
       <c r="C1957" t="n">
         <v>2.732469858038186</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.289677414981729</v>
+        <v>-4.452366444175641</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.016242467731747</v>
+        <v>0.9511668560541828</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.3812563381445147</v>
+        <v>-0.5215846481183792</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.503716055151478</v>
+        <v>2.419519069167159</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.822026809697184</v>
+        <v>3.83129192242654</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.917745580487016</v>
+        <v>2.842797347970488</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.289677414981729</v>
+        <v>-4.452366444175641</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.016242467731747</v>
+        <v>0.9511668560541828</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.3812563381445147</v>
+        <v>-0.5215846481183792</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.910809377473384</v>
+        <v>2.835861144956856</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240508.xlsx
+++ b/tame_output/ON/bt/strategyON_20240508.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>47.0%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.4%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-6.3%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-27.3%</t>
+          <t>-40.3%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.6%</t>
+          <t>-79.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>113.8%</t>
+          <t>114.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>134.3%</t>
+          <t>135.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.3%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-56.4%</t>
+          <t>-57.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.0%</t>
+          <t>-76.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>94.5%</t>
+          <t>95.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.0%</t>
+          <t>444.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.3%</t>
+          <t>-8.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-606.8%</t>
+          <t>-607.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1155,27 +1155,27 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-44.1%</t>
+          <t>-44.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2.0%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-77.8%</t>
+          <t>-77.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>5.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-281.1%</t>
+          <t>-283.5%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-31.2%</t>
+          <t>-30.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>69.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-25.3%</t>
+          <t>-24.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-158.6%</t>
+          <t>-155.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-276.2%</t>
+          <t>-265.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.6%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-162.4%</t>
+          <t>-199.8%</t>
         </is>
       </c>
     </row>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.206837707120693</v>
+        <v>-8.344904506371099</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1681132483236407</v>
+        <v>-0.2233399680238031</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.741209520764524</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.368979977583786</v>
+        <v>-8.507046776834192</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2345652364538768</v>
+        <v>-0.2897919561540396</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.741209520764524</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969596</v>
+        <v>3.424633354969595</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.665641319393984</v>
+        <v>-8.803708118644391</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3494507972487479</v>
+        <v>-0.4046775169489107</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.809952656498403</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923089</v>
+        <v>3.419979433923088</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.098990427504219</v>
+        <v>-9.237057226754626</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.5268167450272454</v>
+        <v>-0.5820434647274078</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.809952656498403</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.48199181624685</v>
+        <v>-9.620058615497257</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.6801194018458818</v>
+        <v>-0.7353461215460442</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.809952656498403</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317619</v>
+        <v>3.447750501317618</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.639390696459971</v>
+        <v>-9.777457495710378</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.7405074379597001</v>
+        <v>-0.7957341576598624</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.967351536711524</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737172</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.998921018963973</v>
+        <v>-10.13698781821438</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.8789692636632505</v>
+        <v>-0.9341959833634128</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.967351536711524</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341316</v>
+        <v>3.503170282341315</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.32532104762899</v>
+        <v>-10.46338784687939</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.001613255172078</v>
+        <v>-1.05683997487224</v>
       </c>
       <c r="F1875" t="n">
         <v>-2.293751565376537</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776679</v>
+        <v>3.500446096776678</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.54447001570318</v>
+        <v>-10.68253681495359</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.086231091779988</v>
+        <v>-1.141457811480151</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.512900533450734</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.54077909074677</v>
+        <v>-10.67884588999718</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.084754721797424</v>
+        <v>-1.139981441497586</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.512900533450734</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611698</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.74503726607664</v>
+        <v>-10.88310406532704</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.160944794810727</v>
+        <v>-1.21617151451089</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.640539478064723</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199889</v>
+        <v>3.496848329199888</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.96307503770781</v>
+        <v>-11.10114183695822</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.243677348978762</v>
+        <v>-1.298904068678925</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.815310246160622</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910632</v>
+        <v>3.499968163910631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.88960520604036</v>
+        <v>-11.02767200529077</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.198917714818362</v>
+        <v>-1.254144434518524</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.741840414493173</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.06472962342691</v>
+        <v>-11.20279642267731</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.254412261025462</v>
+        <v>-1.309638980725625</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.916964831879717</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.48587501888027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.2991817174414</v>
+        <v>-11.4372485166918</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.355412263532854</v>
+        <v>-1.410638983233016</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.916964831879717</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234397</v>
+        <v>3.480688917234396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.58698556197864</v>
+        <v>-11.72505236122904</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.477205992121725</v>
+        <v>-1.532432711821888</v>
       </c>
       <c r="F1883" t="n">
         <v>-3.204768676416955</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.493712438860585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.81681000914246</v>
+        <v>-11.95487680839287</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.568019981148699</v>
+        <v>-1.623246700848862</v>
       </c>
       <c r="F1884" t="n">
         <v>-3.367416213487116</v>
@@ -44906,10 +44906,10 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.04883892887872</v>
+        <v>-12.18690572812913</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.658137820414089</v>
+        <v>-1.713364540114252</v>
       </c>
       <c r="F1885" t="n">
         <v>-3.429428910675539</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.99682341490991</v>
+        <v>-12.13489021416032</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.633341279140163</v>
+        <v>-1.688567998840326</v>
       </c>
       <c r="F1886" t="n">
         <v>-3.429428910675539</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.60003468962892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.13849525663403</v>
+        <v>-12.27656205588444</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.691485242728553</v>
+        <v>-1.746711962428716</v>
       </c>
       <c r="F1887" t="n">
         <v>-3.429428910675539</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410718</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.0889044122092</v>
+        <v>-12.2269712114596</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.656595494793747</v>
+        <v>-1.71182221449391</v>
       </c>
       <c r="F1888" t="n">
         <v>-3.379838066250705</v>
@@ -44998,10 +44998,10 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.8897523049721</v>
+        <v>-12.0278191042225</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.58998578554559</v>
+        <v>-1.645212505245753</v>
       </c>
       <c r="F1889" t="n">
         <v>-3.214515540300892</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085281</v>
+        <v>3.68515780608528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.66390715225269</v>
+        <v>-11.80197395150309</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.490068651421617</v>
+        <v>-1.54529537112178</v>
       </c>
       <c r="F1890" t="n">
         <v>-3.172588864713728</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282102</v>
+        <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.5393284959151</v>
+        <v>-11.6773952951655</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.439098044330521</v>
+        <v>-1.494324764030684</v>
       </c>
       <c r="F1891" t="n">
         <v>-3.172588864713728</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116217</v>
+        <v>3.710931958116216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.59222378395938</v>
+        <v>-11.73029058320979</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.457622385386129</v>
+        <v>-1.512849105086292</v>
       </c>
       <c r="F1892" t="n">
         <v>-3.167633518625282</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081569</v>
+        <v>3.768948099081568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.30831505303063</v>
+        <v>-11.44638185228104</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.338325188775992</v>
+        <v>-1.393551908476155</v>
       </c>
       <c r="F1893" t="n">
         <v>-3.167633518625282</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425328</v>
+        <v>3.728574354425327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.23694866042099</v>
+        <v>-11.37501545967139</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.319515894125999</v>
+        <v>-1.374742613826162</v>
       </c>
       <c r="F1894" t="n">
         <v>-3.096267126015634</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702412</v>
+        <v>3.747699084702411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.97311179321692</v>
+        <v>-11.11117859246732</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.223864628557279</v>
+        <v>-1.279091348257441</v>
       </c>
       <c r="F1895" t="n">
         <v>-3.096267126015634</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906228</v>
+        <v>3.766313503906227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.70586999234852</v>
+        <v>-10.84393679159892</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.118802468709294</v>
+        <v>-1.174029188409456</v>
       </c>
       <c r="F1896" t="n">
         <v>-3.096267126015634</v>
@@ -45182,10 +45182,10 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.60796295367203</v>
+        <v>-10.74602975292243</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.079939968212158</v>
+        <v>-1.13516668791232</v>
       </c>
       <c r="F1897" t="n">
         <v>-3.028281376155078</v>
@@ -45205,10 +45205,10 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.58400941269607</v>
+        <v>-10.72207621194648</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.069690045676281</v>
+        <v>-1.124916765376443</v>
       </c>
       <c r="F1898" t="n">
         <v>-3.00432783517912</v>
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487773</v>
+        <v>3.789307536487772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.46027778434714</v>
+        <v>-10.45801627362368</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.03345771049846</v>
+        <v>-1.032553106209077</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.880596206830189</v>
+        <v>-2.740267896856324</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.422652103456029</v>
+        <v>1.506849089440348</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309726</v>
+        <v>3.833249172309725</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.753198160842301</v>
+        <v>-9.750936650118842</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7534128947568268</v>
+        <v>-0.7525082904674432</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.880596206830189</v>
+        <v>-2.740267896856324</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.419865069795728</v>
+        <v>1.504062055780047</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858729</v>
+        <v>3.839370871858728</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.71301386247611</v>
+        <v>-9.710752351752651</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7369955515225093</v>
+        <v>-0.7360909472331256</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.840411908463998</v>
+        <v>-2.700083598490133</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.444319272703284</v>
+        <v>1.528516258687603</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096475</v>
+        <v>3.856158176096473</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.632944066938306</v>
+        <v>-9.630682556214847</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.7056008120866304</v>
+        <v>-0.7046962077972467</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.760342112926194</v>
+        <v>-2.620013802952329</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.491727971246723</v>
+        <v>1.575924957231042</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78732685376181</v>
+        <v>3.787326853761808</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.399462844708708</v>
+        <v>-9.397201333985247</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.6042838943569389</v>
+        <v>-0.6033792900675548</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.526860890696595</v>
+        <v>-2.386532580722731</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.639741133422335</v>
+        <v>1.723938119406654</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255787</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.219754314564835</v>
+        <v>-9.217492803841374</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5352926926123489</v>
+        <v>-0.5343880883229644</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.469689386533899</v>
+        <v>-2.329361076560035</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.671151825606993</v>
+        <v>1.755348811591312</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860429</v>
+        <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.087478840933947</v>
+        <v>-9.085217330210487</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.487015016412967</v>
+        <v>-0.4861104121235824</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.337413912903013</v>
+        <v>-2.197085602929148</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.745884596532552</v>
+        <v>1.830081582516871</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575955</v>
+        <v>3.784715218575953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.896879166260794</v>
+        <v>-8.894617655537333</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.4079600858560686</v>
+        <v>-0.4070554815666845</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.14681423822986</v>
+        <v>-2.006485928255995</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.86305946202408</v>
+        <v>1.947256448008399</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430989</v>
+        <v>3.753878996430987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.647879367577213</v>
+        <v>-8.645617856853752</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2954538251589773</v>
+        <v>-0.2945492208695932</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.14681423822986</v>
+        <v>-2.006485928255995</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.875965803247739</v>
+        <v>1.960162789232058</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077645</v>
+        <v>3.692928280077643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.753469357350317</v>
+        <v>-8.751207846626857</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.465665750667438</v>
+        <v>-0.4647611463780539</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.252404228002965</v>
+        <v>-2.1120759180291</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.684635879784658</v>
+        <v>1.768832865768977</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457903</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.772204259468914</v>
+        <v>-8.769942748745454</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4246153696377903</v>
+        <v>-0.4237107653484062</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.252404228002965</v>
+        <v>-2.1120759180291</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.733180221661744</v>
+        <v>1.817377207646063</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180811</v>
+        <v>3.760330111180809</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.624264218061315</v>
+        <v>-8.622002707337854</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.4853182757629182</v>
+        <v>-0.4844136714735341</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.232083312094407</v>
+        <v>-2.091755002120542</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.625493848518711</v>
+        <v>1.70969083450303</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879204</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.600035581672342</v>
+        <v>-8.597774070948882</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.4843408074608075</v>
+        <v>-0.483436203171423</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.207854675705435</v>
+        <v>-2.06752636573157</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.631317044098616</v>
+        <v>1.715514030082935</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568109</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.556487174901651</v>
+        <v>-8.55422566417819</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.4738820568476241</v>
+        <v>-0.47297745255824</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.207854675705435</v>
+        <v>-2.06752636573157</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.624356432003523</v>
+        <v>1.708553417987842</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.78291895796342</v>
+        <v>3.782918957963418</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.314338781447793</v>
+        <v>-8.312077270724332</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3625603450849377</v>
+        <v>-0.3616557407955536</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.207854675705435</v>
+        <v>-2.06752636573157</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.638818786384666</v>
+        <v>1.723015772368985</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192818</v>
+        <v>3.828547911192817</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.251109409679446</v>
+        <v>-8.248847898955985</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.3427364759184037</v>
+        <v>-0.3418318716290196</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.207854675705435</v>
+        <v>-2.06752636573157</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.633350906843861</v>
+        <v>1.71754789282818</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262049</v>
+        <v>3.828049353262047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.127818274862316</v>
+        <v>-8.125556764138855</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.2959219279809751</v>
+        <v>-0.2950173236915905</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.084563540888305</v>
+        <v>-1.94423523091444</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.704823681744716</v>
+        <v>1.789020667729035</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389911</v>
+        <v>3.812450103389909</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-8.106669075958873</v>
+        <v>-8.104407565235412</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.2797612701822727</v>
+        <v>-0.2788566658928886</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.063414341984861</v>
+        <v>-1.923086032010997</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.725214179324108</v>
+        <v>1.809411165308426</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788096</v>
+        <v>3.748324832788094</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.862903633975429</v>
+        <v>-7.860642123251968</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.1864743850418442</v>
+        <v>-0.1855697807524601</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.063414341984861</v>
+        <v>-1.923086032010997</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.720994887671158</v>
+        <v>1.805191873655477</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527527</v>
+        <v>3.824307657527525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.598875566782169</v>
+        <v>-7.596614056058709</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.07873884424452449</v>
+        <v>-0.07783423995514038</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.861548943168908</v>
+        <v>-1.721220633195043</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.844238440880746</v>
+        <v>1.928435426865065</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749186</v>
+        <v>3.826351398749184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.349025172833095</v>
+        <v>-7.346763662109634</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.01394338831880759</v>
+        <v>0.0148479926081917</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.861548943168908</v>
+        <v>-1.721220633195043</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.836980515864449</v>
+        <v>1.921177501848767</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481499</v>
+        <v>3.835954411481497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.173133080365663</v>
+        <v>-7.170871569642202</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.08789934882642925</v>
+        <v>0.08880395311581335</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.861548943168908</v>
+        <v>-1.721220633195043</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.840579639385097</v>
+        <v>1.924776625369416</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862989</v>
+        <v>3.780930335862987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-7.001686617343199</v>
+        <v>-6.999425106619738</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.1698054400899682</v>
+        <v>0.1707100443793523</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.690102480146444</v>
+        <v>-1.54977417017258</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.956775023253129</v>
+        <v>2.040972009237448</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102783</v>
+        <v>3.773761647102782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.776653617674376</v>
+        <v>-6.774392106950915</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.2588391175737943</v>
+        <v>0.2597437218631784</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.465069480477621</v>
+        <v>-1.324741170503757</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.09081530067072</v>
+        <v>2.175012286655038</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353076</v>
+        <v>3.764614304353074</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.562019240037969</v>
+        <v>-6.559757729314509</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.3493876696826743</v>
+        <v>0.3502922739720584</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.250435102841215</v>
+        <v>-1.11010679286735</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.224290728306881</v>
+        <v>2.3084877142912</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544785</v>
+        <v>3.798811195544783</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.469019198832071</v>
+        <v>-6.46675768810861</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.3677819449488293</v>
+        <v>0.3686865492382134</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.250435102841215</v>
+        <v>-1.11010679286735</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.205484987090677</v>
+        <v>2.289681973074996</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712296</v>
+        <v>3.797691308712294</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.228588702027211</v>
+        <v>-6.22632719130375</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.4656972202956506</v>
+        <v>0.4666018245850352</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.010004606036354</v>
+        <v>-0.8696762960624898</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.35148636179847</v>
+        <v>2.435683347782789</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837687</v>
+        <v>3.821589933837686</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-6.156346133856016</v>
+        <v>-6.154084623132555</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.4985235613989487</v>
+        <v>0.4994281656883333</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.010004606036354</v>
+        <v>-0.8696762960624898</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.35541567563329</v>
+        <v>2.439612661617609</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349969</v>
+        <v>3.822323422349966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-6.040406284230831</v>
+        <v>-6.045330698947253</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.5455780851663627</v>
+        <v>0.543608319279794</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.9331828750202305</v>
+        <v>-0.810885510187682</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.402187298160305</v>
+        <v>2.475565717059834</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972342</v>
+        <v>3.84861305097234</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.797750695807668</v>
+        <v>-5.80267511052409</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.6396383917556214</v>
+        <v>0.6376686258690527</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.9331828750202305</v>
+        <v>-0.810885510187682</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.399185369380298</v>
+        <v>2.472563788279827</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145941</v>
+        <v>3.818665376145939</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.577729897770658</v>
+        <v>-5.58265431248708</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.7292257479810398</v>
+        <v>0.7272559820944711</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.7919630299522502</v>
+        <v>-0.6696656651197017</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.485496313431701</v>
+        <v>2.558874732331229</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009953</v>
+        <v>3.84327095200995</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.378481267865848</v>
+        <v>-5.38340568258227</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.8248193827447867</v>
+        <v>0.822849616858218</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.7919630299522502</v>
+        <v>-0.6696656651197017</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.501390496233524</v>
+        <v>2.574768915133053</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966262</v>
+        <v>3.845043810966259</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.218966164346479</v>
+        <v>-5.223890579062901</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.8897712685928365</v>
+        <v>0.8878015027062678</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.6324479264328803</v>
+        <v>-0.5101505616003318</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.598245402785448</v>
+        <v>2.671623821684977</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046999</v>
+        <v>3.791269976046996</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-5.074294019246741</v>
+        <v>-5.079218433963163</v>
       </c>
       <c r="E1932" t="n">
-        <v>0.9577282291941716</v>
+        <v>0.9557584633076028</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.4877757813331429</v>
+        <v>-0.3654784165005944</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.69513679240673</v>
+        <v>2.768515211306259</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412106</v>
+        <v>3.735835647412103</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-5.134168846604434</v>
+        <v>-5.139093261320856</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9198157896525205</v>
+        <v>0.9178460237659518</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.547650608690835</v>
+        <v>-0.4253532438582865</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.645249387393541</v>
+        <v>2.718627806293069</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144519</v>
+        <v>3.762643902144516</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-5.047369348825425</v>
+        <v>-5.052293763541847</v>
       </c>
       <c r="E1934" t="n">
-        <v>0.9769360820866897</v>
+        <v>0.974966316200121</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.547650608690835</v>
+        <v>-0.4253532438582865</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.667649880716107</v>
+        <v>2.741028299615635</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900696</v>
+        <v>3.729142822900693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-5.049839055287231</v>
+        <v>-5.054763470003653</v>
       </c>
       <c r="E1935" t="n">
-        <v>0.9760206008753798</v>
+        <v>0.9740508349888106</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.5501203151526413</v>
+        <v>-0.4278229503200927</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.666240458212435</v>
+        <v>2.739618877111964</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473603</v>
+        <v>3.7432166204736</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-5.118209241611241</v>
+        <v>-5.123133656327663</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.9596794488204776</v>
+        <v>0.9577096829339089</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.5408446161164263</v>
+        <v>-0.4185472512838777</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.682812800108866</v>
+        <v>2.756191219008395</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978372</v>
+        <v>3.714175563978369</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.996792811984765</v>
+        <v>-5.001717226701187</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9986827293029594</v>
+        <v>0.9967129634163907</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.5408446161164263</v>
+        <v>-0.4185472512838777</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.673249508740757</v>
+        <v>2.746627927640287</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887706</v>
+        <v>3.710903155887703</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.02778597131347</v>
+        <v>-5.032710386029892</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8109950306118643</v>
+        <v>0.8090252647252951</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.5408446161164263</v>
+        <v>-0.4185472512838777</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.497959073781144</v>
+        <v>2.571337492680673</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675904</v>
+        <v>3.7460389506759</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.852311711521001</v>
+        <v>-4.857236126237423</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.8857519665206397</v>
+        <v>0.883782200634071</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.5408446161164263</v>
+        <v>-0.4185472512838777</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.502526305772932</v>
+        <v>2.575904724672461</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695448</v>
+        <v>3.765020747695445</v>
       </c>
       <c r="C1940" t="n">
         <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.96324796416225</v>
+        <v>-4.968172378878672</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8413889393509377</v>
+        <v>0.839419173464369</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.5408446161164263</v>
+        <v>-0.4185472512838777</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.502537779659729</v>
+        <v>2.575916198559258</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581294</v>
+        <v>3.773206721581291</v>
       </c>
       <c r="C1941" t="n">
         <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.166274541705483</v>
+        <v>-5.171198956421905</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.7633096935535502</v>
+        <v>0.761339927666981</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.7438711936596597</v>
+        <v>-0.6215738288271111</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.383853218353695</v>
+        <v>2.457231637253224</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734163</v>
+        <v>3.78434037673416</v>
       </c>
       <c r="C1942" t="n">
         <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-5.00834894277019</v>
+        <v>-5.013273357486612</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8366523195597995</v>
+        <v>0.8346825536732307</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.7438711936596597</v>
+        <v>-0.6215738288271111</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.394025604785827</v>
+        <v>2.467404023685356</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869463822123</v>
+        <v>3.786946382212296</v>
       </c>
       <c r="C1943" t="n">
         <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-5.156670196581318</v>
+        <v>-5.16159461129774</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.7722700886092082</v>
+        <v>0.7703003227226395</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.7438711936596597</v>
+        <v>-0.6215738288271111</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.388971875359688</v>
+        <v>2.462350294259217</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786047</v>
+        <v>3.752023923786044</v>
       </c>
       <c r="C1944" t="n">
         <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-5.157853281232379</v>
+        <v>-5.162777695948801</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.7635726301933099</v>
+        <v>0.7616028643067407</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.7495142421261712</v>
+        <v>-0.6272168772936226</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.377361821724306</v>
+        <v>2.450740240623835</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273192</v>
+        <v>3.753567590273189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-5.034725574238296</v>
+        <v>-5.039649988954718</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8133755860240446</v>
+        <v>0.8114058201374759</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.7495142421261712</v>
+        <v>-0.6272168772936226</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.377913694757408</v>
+        <v>2.451292113656937</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279502</v>
+        <v>3.733387025279498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.941915092787436</v>
+        <v>-4.946839507503858</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.779772470495754</v>
+        <v>0.7778027046091851</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.6567037606753119</v>
+        <v>-0.5344063958427633</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.362872675519289</v>
+        <v>2.436251094418818</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030429</v>
+        <v>3.748282241030426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.893352040566406</v>
+        <v>-4.898276455282828</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8010711673087667</v>
+        <v>0.799101401422198</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.6081407084542817</v>
+        <v>-0.4858433436217331</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.393883982776508</v>
+        <v>2.467262401676037</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942741</v>
+        <v>3.721073619942738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.7538441163608</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.780680822330156</v>
+        <v>-4.785605237046578</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8412153631149899</v>
+        <v>0.839245597228421</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.4954694902180315</v>
+        <v>-0.3731721253854829</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.456562422229981</v>
+        <v>2.52994084112951</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268539</v>
+        <v>3.743044028268535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.759335412191467</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.668303821147483</v>
+        <v>-4.673228235863905</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.8916574594187263</v>
+        <v>0.8896876935321574</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.4954694902180315</v>
+        <v>-0.3731721253854829</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.462053718060648</v>
+        <v>2.535432136960178</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968865</v>
+        <v>3.689594264968861</v>
       </c>
       <c r="C1950" t="n">
         <v>2.770832613960006</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.866538390034214</v>
+        <v>-4.871462804750636</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.823860833632573</v>
+        <v>0.8218910677460043</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.6937040591047621</v>
+        <v>-0.5714066942722135</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.354610178497149</v>
+        <v>2.427988597396678</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175325</v>
+        <v>3.643066046175321</v>
       </c>
       <c r="C1951" t="n">
         <v>2.609188333960659</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.949539671059493</v>
+        <v>-4.954464085775915</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6290160412231147</v>
+        <v>0.627046275336546</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.7122749436319358</v>
+        <v>-0.5899775787993873</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.181823367781498</v>
+        <v>2.255201786681027</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199272</v>
+        <v>3.682712735199268</v>
       </c>
       <c r="C1952" t="n">
         <v>2.729337994679865</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.790345399002916</v>
+        <v>-4.795269813719338</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8128434107649509</v>
+        <v>0.8108736448783822</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.7122749436319358</v>
+        <v>-0.5899775787993873</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.301973028500703</v>
+        <v>2.375351447400233</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660771</v>
+        <v>3.733008865660768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.743851020782188</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.876943981984019</v>
+        <v>-4.881868396700441</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7927170036748328</v>
+        <v>0.7907472377882641</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.7122749436319358</v>
+        <v>-0.5899775787993873</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.316486054603026</v>
+        <v>2.389864473502556</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383427</v>
+        <v>3.741170494383423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.741270462124556</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.838560319425868</v>
+        <v>-4.84348473414229</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.805489910040462</v>
+        <v>0.8035201441538931</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.6738912810737846</v>
+        <v>-0.5515939162412361</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.336935693480286</v>
+        <v>2.410314112379815</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002488</v>
+        <v>3.751143622002484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.737999490969859</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.661443989390702</v>
+        <v>-4.666368404107124</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8730654708998307</v>
+        <v>0.8710957050132619</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.6738912810737846</v>
+        <v>-0.5515939162412361</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.333664722325588</v>
+        <v>2.407043141225118</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263905</v>
+        <v>3.741324873263902</v>
       </c>
       <c r="C1956" t="n">
         <v>2.738682882731772</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.631741865414408</v>
+        <v>-4.63666628013083</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8856297122522614</v>
+        <v>0.8836599463656925</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.6783614062890979</v>
+        <v>-0.5560640414565494</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.331666038958313</v>
+        <v>2.405044457857842</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.735861515710479</v>
+        <v>3.735861515710476</v>
       </c>
       <c r="C1957" t="n">
         <v>2.732469858038186</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.452366444175641</v>
+        <v>-4.457290858892063</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9511668560541828</v>
+        <v>0.9491970901676139</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.5215846481183792</v>
+        <v>-0.3992872832858307</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.419519069167159</v>
+        <v>2.492897488066688</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.83129192242654</v>
+        <v>3.750553060213925</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.842797347970488</v>
+        <v>2.713277313369776</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.452366444175641</v>
+        <v>-4.463064214317029</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9511668560541828</v>
+        <v>0.9276952033292172</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.5215846481183792</v>
+        <v>-0.4191641935794213</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.835861144956856</v>
+        <v>2.461778797222124</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240508.xlsx
+++ b/tame_output/ON/bt/strategyON_20240508.xlsx
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-6.3%</t>
+          <t>-6.2%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-40.3%</t>
+          <t>-40.0%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.9%</t>
+          <t>-79.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>114.8%</t>
+          <t>114.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>92.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.0%</t>
+          <t>-56.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.4%</t>
+          <t>-75.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>95.3%</t>
+          <t>95.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.5%</t>
+          <t>444.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-607.9%</t>
+          <t>-593.8%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-77.4%</t>
+          <t>-73.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-283.5%</t>
+          <t>-277.5%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-30.1%</t>
+          <t>-28.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-24.2%</t>
+          <t>-22.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>40.1%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-265.9%</t>
+          <t>-253.7%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-199.8%</t>
+          <t>-192.2%</t>
         </is>
       </c>
     </row>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.507046776834192</v>
+        <v>-8.486575352920964</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2897919561540396</v>
+        <v>-0.2816033865887482</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.741209520764524</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.803708118644391</v>
+        <v>-8.783236694731162</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.4046775169489107</v>
+        <v>-0.3964889473836193</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.809952656498403</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.237057226754626</v>
+        <v>-9.216585802841397</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.5820434647274078</v>
+        <v>-0.5738548951621163</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.809952656498403</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.620058615497257</v>
+        <v>-9.599587191584028</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.7353461215460442</v>
+        <v>-0.7271575519807527</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.809952656498403</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.777457495710378</v>
+        <v>-9.756986071797149</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.7957341576598624</v>
+        <v>-0.787545588094571</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.967351536711524</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.13698781821438</v>
+        <v>-10.11651639430115</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.9341959833634128</v>
+        <v>-0.9260074137981213</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.967351536711524</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.46338784687939</v>
+        <v>-10.44291642296616</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.05683997487224</v>
+        <v>-1.048651405306949</v>
       </c>
       <c r="F1875" t="n">
         <v>-2.293751565376537</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.68253681495359</v>
+        <v>-10.66206539104036</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.141457811480151</v>
+        <v>-1.13326924191486</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.512900533450734</v>
@@ -44722,10 +44722,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.67884588999718</v>
+        <v>-10.65837446608395</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.139981441497586</v>
+        <v>-1.131792871932295</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.512900533450734</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.88310406532704</v>
+        <v>-10.86263264141381</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.21617151451089</v>
+        <v>-1.207982944945599</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.640539478064723</v>
@@ -44768,10 +44768,10 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.10114183695822</v>
+        <v>-11.08067041304499</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.298904068678925</v>
+        <v>-1.290715499113633</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.815310246160622</v>
@@ -44791,10 +44791,10 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.02767200529077</v>
+        <v>-11.00720058137754</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.254144434518524</v>
+        <v>-1.245955864953232</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.741840414493173</v>
@@ -44814,10 +44814,10 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.20279642267731</v>
+        <v>-11.18232499876409</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.309638980725625</v>
+        <v>-1.301450411160333</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.916964831879717</v>
@@ -44837,10 +44837,10 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.4372485166918</v>
+        <v>-11.41677709277858</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.410638983233016</v>
+        <v>-1.402450413667724</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.916964831879717</v>
@@ -44860,10 +44860,10 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.72505236122904</v>
+        <v>-11.70458093731581</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.532432711821888</v>
+        <v>-1.524244142256597</v>
       </c>
       <c r="F1883" t="n">
         <v>-3.204768676416955</v>
@@ -44883,10 +44883,10 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.95487680839287</v>
+        <v>-11.93440538447964</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.623246700848862</v>
+        <v>-1.61505813128357</v>
       </c>
       <c r="F1884" t="n">
         <v>-3.367416213487116</v>
@@ -44906,10 +44906,10 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.18690572812913</v>
+        <v>-12.1664343042159</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.713364540114252</v>
+        <v>-1.70517597054896</v>
       </c>
       <c r="F1885" t="n">
         <v>-3.429428910675539</v>
@@ -44929,10 +44929,10 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.13489021416032</v>
+        <v>-12.11441879024709</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.688567998840326</v>
+        <v>-1.680379429275034</v>
       </c>
       <c r="F1886" t="n">
         <v>-3.429428910675539</v>
@@ -44952,10 +44952,10 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.27656205588444</v>
+        <v>-12.25609063197121</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.746711962428716</v>
+        <v>-1.738523392863424</v>
       </c>
       <c r="F1887" t="n">
         <v>-3.429428910675539</v>
@@ -44975,10 +44975,10 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.2269712114596</v>
+        <v>-12.20649978754637</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.71182221449391</v>
+        <v>-1.703633644928618</v>
       </c>
       <c r="F1888" t="n">
         <v>-3.379838066250705</v>
@@ -44998,10 +44998,10 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.0278191042225</v>
+        <v>-12.00734768030927</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.645212505245753</v>
+        <v>-1.637023935680462</v>
       </c>
       <c r="F1889" t="n">
         <v>-3.214515540300892</v>
@@ -45021,10 +45021,10 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.80197395150309</v>
+        <v>-11.78150252758986</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.54529537112178</v>
+        <v>-1.537106801556489</v>
       </c>
       <c r="F1890" t="n">
         <v>-3.172588864713728</v>
@@ -45044,10 +45044,10 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.6773952951655</v>
+        <v>-11.65692387125227</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.494324764030684</v>
+        <v>-1.486136194465393</v>
       </c>
       <c r="F1891" t="n">
         <v>-3.172588864713728</v>
@@ -45067,10 +45067,10 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.73029058320979</v>
+        <v>-11.70981915929656</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.512849105086292</v>
+        <v>-1.504660535521</v>
       </c>
       <c r="F1892" t="n">
         <v>-3.167633518625282</v>
@@ -45090,10 +45090,10 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.44638185228104</v>
+        <v>-11.42591042836781</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.393551908476155</v>
+        <v>-1.385363338910864</v>
       </c>
       <c r="F1893" t="n">
         <v>-3.167633518625282</v>
@@ -45113,10 +45113,10 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.37501545967139</v>
+        <v>-11.35454403575816</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.374742613826162</v>
+        <v>-1.36655404426087</v>
       </c>
       <c r="F1894" t="n">
         <v>-3.096267126015634</v>
@@ -45136,10 +45136,10 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.11117859246732</v>
+        <v>-11.09070716855409</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.279091348257441</v>
+        <v>-1.27090277869215</v>
       </c>
       <c r="F1895" t="n">
         <v>-3.096267126015634</v>
@@ -45159,10 +45159,10 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.84393679159892</v>
+        <v>-10.8234653676857</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.174029188409456</v>
+        <v>-1.165840618844164</v>
       </c>
       <c r="F1896" t="n">
         <v>-3.096267126015634</v>
@@ -45182,10 +45182,10 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.74602975292243</v>
+        <v>-10.72555832900921</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.13516668791232</v>
+        <v>-1.126978118347029</v>
       </c>
       <c r="F1897" t="n">
         <v>-3.028281376155078</v>
@@ -45205,10 +45205,10 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.72207621194648</v>
+        <v>-10.70160478803325</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.124916765376443</v>
+        <v>-1.116728195811152</v>
       </c>
       <c r="F1898" t="n">
         <v>-3.00432783517912</v>
@@ -45228,10 +45228,10 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.45801627362368</v>
+        <v>-10.43754484971045</v>
       </c>
       <c r="E1899" t="n">
-        <v>-1.032553106209077</v>
+        <v>-1.024364536643786</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.740267896856324</v>
@@ -45251,10 +45251,10 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.750936650118842</v>
+        <v>-9.730465226205613</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7525082904674432</v>
+        <v>-0.7443197209021517</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.740267896856324</v>
@@ -45274,10 +45274,10 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.710752351752651</v>
+        <v>-9.690280927839423</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7360909472331256</v>
+        <v>-0.7279023776678342</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.700083598490133</v>
@@ -45297,10 +45297,10 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.630682556214847</v>
+        <v>-9.610211132301618</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.7046962077972467</v>
+        <v>-0.6965076382319553</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.620013802952329</v>
@@ -45320,10 +45320,10 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.397201333985247</v>
+        <v>-9.376729910072019</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.6033792900675548</v>
+        <v>-0.5951907205022633</v>
       </c>
       <c r="F1903" t="n">
         <v>-2.386532580722731</v>
@@ -45343,10 +45343,10 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.217492803841374</v>
+        <v>-9.197021379928145</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5343880883229644</v>
+        <v>-0.5261995187576729</v>
       </c>
       <c r="F1904" t="n">
         <v>-2.329361076560035</v>
@@ -45366,10 +45366,10 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-9.085217330210487</v>
+        <v>-9.064745906297258</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4861104121235824</v>
+        <v>-0.477921842558291</v>
       </c>
       <c r="F1905" t="n">
         <v>-2.197085602929148</v>
@@ -45389,10 +45389,10 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.894617655537333</v>
+        <v>-8.874146231624104</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.4070554815666845</v>
+        <v>-0.398866912001393</v>
       </c>
       <c r="F1906" t="n">
         <v>-2.006485928255995</v>
@@ -45412,10 +45412,10 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.645617856853752</v>
+        <v>-8.625146432940523</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2945492208695932</v>
+        <v>-0.2863606513043018</v>
       </c>
       <c r="F1907" t="n">
         <v>-2.006485928255995</v>
@@ -45435,10 +45435,10 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.751207846626857</v>
+        <v>-8.730736422713628</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4647611463780539</v>
+        <v>-0.4565725768127624</v>
       </c>
       <c r="F1908" t="n">
         <v>-2.1120759180291</v>
@@ -45458,10 +45458,10 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.769942748745454</v>
+        <v>-8.749471324832225</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.4237107653484062</v>
+        <v>-0.4155221957831148</v>
       </c>
       <c r="F1909" t="n">
         <v>-2.1120759180291</v>
@@ -45481,10 +45481,10 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.622002707337854</v>
+        <v>-8.601531283424626</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.4844136714735341</v>
+        <v>-0.4762251019082426</v>
       </c>
       <c r="F1910" t="n">
         <v>-2.091755002120542</v>
@@ -45504,10 +45504,10 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.597774070948882</v>
+        <v>-8.577302647035653</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.483436203171423</v>
+        <v>-0.4752476336061315</v>
       </c>
       <c r="F1911" t="n">
         <v>-2.06752636573157</v>
@@ -45527,10 +45527,10 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.55422566417819</v>
+        <v>-8.533754240264962</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.47297745255824</v>
+        <v>-0.4647888829929485</v>
       </c>
       <c r="F1912" t="n">
         <v>-2.06752636573157</v>
@@ -45550,10 +45550,10 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.312077270724332</v>
+        <v>-8.291605846811104</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.3616557407955536</v>
+        <v>-0.3534671712302622</v>
       </c>
       <c r="F1913" t="n">
         <v>-2.06752636573157</v>
@@ -45573,10 +45573,10 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.248847898955985</v>
+        <v>-8.228376475042756</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.3418318716290196</v>
+        <v>-0.3336433020637282</v>
       </c>
       <c r="F1914" t="n">
         <v>-2.06752636573157</v>
@@ -45596,10 +45596,10 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-8.125556764138855</v>
+        <v>-8.105085340225626</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.2950173236915905</v>
+        <v>-0.286828754126299</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.94423523091444</v>
@@ -45619,10 +45619,10 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-8.104407565235412</v>
+        <v>-8.083936141322184</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.2788566658928886</v>
+        <v>-0.2706680963275971</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.923086032010997</v>
@@ -45642,10 +45642,10 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.860642123251968</v>
+        <v>-7.840170699338739</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.1855697807524601</v>
+        <v>-0.1773812111871687</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.923086032010997</v>
@@ -45665,10 +45665,10 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.596614056058709</v>
+        <v>-7.57614263214548</v>
       </c>
       <c r="E1918" t="n">
-        <v>-0.07783423995514038</v>
+        <v>-0.06964567038984892</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.721220633195043</v>
@@ -45688,10 +45688,10 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.346763662109634</v>
+        <v>-7.326292238196405</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.0148479926081917</v>
+        <v>0.02303656217348315</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.721220633195043</v>
@@ -45711,10 +45711,10 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-7.170871569642202</v>
+        <v>-7.150400145728973</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.08880395311581335</v>
+        <v>0.09699252268110481</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.721220633195043</v>
@@ -45734,10 +45734,10 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.999425106619738</v>
+        <v>-6.97895368270651</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.1707100443793523</v>
+        <v>0.1788986139446438</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.54977417017258</v>
@@ -45757,10 +45757,10 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.774392106950915</v>
+        <v>-6.753920683037687</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.2597437218631784</v>
+        <v>0.2679322914284699</v>
       </c>
       <c r="F1922" t="n">
         <v>-1.324741170503757</v>
@@ -45780,10 +45780,10 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.559757729314509</v>
+        <v>-6.53928630540128</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.3502922739720584</v>
+        <v>0.3584808435373499</v>
       </c>
       <c r="F1923" t="n">
         <v>-1.11010679286735</v>
@@ -45803,10 +45803,10 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.46675768810861</v>
+        <v>-6.446286264195382</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.3686865492382134</v>
+        <v>0.3768751188035049</v>
       </c>
       <c r="F1924" t="n">
         <v>-1.11010679286735</v>
@@ -45826,10 +45826,10 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-6.22632719130375</v>
+        <v>-6.205855767390521</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.4666018245850352</v>
+        <v>0.4747903941503266</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.8696762960624898</v>
@@ -45849,10 +45849,10 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-6.154084623132555</v>
+        <v>-6.133613199219327</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.4994281656883333</v>
+        <v>0.5076167352536247</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.8696762960624898</v>
@@ -45872,10 +45872,10 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-6.045330698947253</v>
+        <v>-6.024859275034024</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.543608319279794</v>
+        <v>0.5517968888450855</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.810885510187682</v>
@@ -45895,10 +45895,10 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.80267511052409</v>
+        <v>-5.782203686610861</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.6376686258690527</v>
+        <v>0.6458571954343442</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.810885510187682</v>
@@ -45918,10 +45918,10 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.58265431248708</v>
+        <v>-5.562182888573851</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.7272559820944711</v>
+        <v>0.7354445516597625</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.6696656651197017</v>
@@ -45941,10 +45941,10 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.38340568258227</v>
+        <v>-5.362934258669042</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.822849616858218</v>
+        <v>0.8310381864235095</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.6696656651197017</v>
@@ -45964,10 +45964,10 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.223890579062901</v>
+        <v>-5.203419155149672</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.8878015027062678</v>
+        <v>0.8959900722715592</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.5101505616003318</v>
@@ -45987,10 +45987,10 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-5.079218433963163</v>
+        <v>-5.058747010049935</v>
       </c>
       <c r="E1932" t="n">
-        <v>0.9557584633076028</v>
+        <v>0.9639470328728943</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.3654784165005944</v>
@@ -46010,10 +46010,10 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-5.139093261320856</v>
+        <v>-5.118621837407627</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9178460237659518</v>
+        <v>0.9260345933312433</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.4253532438582865</v>
@@ -46033,10 +46033,10 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-5.052293763541847</v>
+        <v>-5.031822339628619</v>
       </c>
       <c r="E1934" t="n">
-        <v>0.974966316200121</v>
+        <v>0.9831548857654124</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.4253532438582865</v>
@@ -46056,10 +46056,10 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-5.054763470003653</v>
+        <v>-5.034292046090425</v>
       </c>
       <c r="E1935" t="n">
-        <v>0.9740508349888106</v>
+        <v>0.9822394045541021</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.4278229503200927</v>
@@ -46079,10 +46079,10 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-5.123133656327663</v>
+        <v>-5.102662232414435</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.9577096829339089</v>
+        <v>0.9658982524992004</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.4185472512838777</v>
@@ -46102,10 +46102,10 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.001717226701187</v>
+        <v>-4.981245802787958</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9967129634163907</v>
+        <v>1.004901532981682</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.4185472512838777</v>
@@ -46125,10 +46125,10 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.032710386029892</v>
+        <v>-5.012238962116664</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8090252647252951</v>
+        <v>0.8172138342905866</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.4185472512838777</v>
@@ -46148,10 +46148,10 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.857236126237423</v>
+        <v>-4.836764702324194</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.883782200634071</v>
+        <v>0.8919707701993624</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.4185472512838777</v>
@@ -46171,10 +46171,10 @@
         <v>2.827044549329585</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.968172378878672</v>
+        <v>-4.947700954965443</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.839419173464369</v>
+        <v>0.8476077430296605</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.4185472512838777</v>
@@ -46194,10 +46194,10 @@
         <v>2.83017593454949</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.171198956421905</v>
+        <v>-5.150727532508676</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.761339927666981</v>
+        <v>0.7695284972322725</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.6215738288271111</v>
@@ -46217,10 +46217,10 @@
         <v>2.840348320981623</v>
       </c>
       <c r="D1942" t="n">
-        <v>-5.013273357486612</v>
+        <v>-4.992801933573383</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8346825536732307</v>
+        <v>0.8428711232385222</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.6215738288271111</v>
@@ -46240,10 +46240,10 @@
         <v>2.835294591555483</v>
       </c>
       <c r="D1943" t="n">
-        <v>-5.16159461129774</v>
+        <v>-5.141123187384512</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.7703003227226395</v>
+        <v>0.7784888922879309</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.6215738288271111</v>
@@ -46263,10 +46263,10 @@
         <v>2.827070367000009</v>
       </c>
       <c r="D1944" t="n">
-        <v>-5.162777695948801</v>
+        <v>-5.142306272035572</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.7616028643067407</v>
+        <v>0.7697914338720322</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.6272168772936226</v>
@@ -46286,10 +46286,10 @@
         <v>2.82762224003311</v>
       </c>
       <c r="D1945" t="n">
-        <v>-5.039649988954718</v>
+        <v>-5.019178565041489</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8114058201374759</v>
+        <v>0.8195943897027673</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.6272168772936226</v>
@@ -46309,10 +46309,10 @@
         <v>2.756894931924476</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.946839507503858</v>
+        <v>-4.92636808359063</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.7778027046091851</v>
+        <v>0.7859912741744766</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.5344063958427633</v>
@@ -46332,10 +46332,10 @@
         <v>2.758768407849077</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.898276455282828</v>
+        <v>-4.8778050313696</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.799101401422198</v>
+        <v>0.8072899709874894</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.4858433436217331</v>
@@ -46355,10 +46355,10 @@
         <v>2.7538441163608</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.785605237046578</v>
+        <v>-4.76513381313335</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.839245597228421</v>
+        <v>0.8474341667937124</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.3731721253854829</v>
@@ -46378,10 +46378,10 @@
         <v>2.759335412191467</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.673228235863905</v>
+        <v>-4.652756811950677</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.8896876935321574</v>
+        <v>0.8978762630974488</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.3731721253854829</v>
@@ -46401,10 +46401,10 @@
         <v>2.770832613960006</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.871462804750636</v>
+        <v>-4.850991380837407</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8218910677460043</v>
+        <v>0.8300796373112957</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.5714066942722135</v>
@@ -46424,10 +46424,10 @@
         <v>2.609188333960659</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.954464085775915</v>
+        <v>-4.933992661862686</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.627046275336546</v>
+        <v>0.6352348449018375</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.5899775787993873</v>
@@ -46447,10 +46447,10 @@
         <v>2.729337994679865</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.795269813719338</v>
+        <v>-4.77479838980611</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8108736448783822</v>
+        <v>0.8190622144436737</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.5899775787993873</v>
@@ -46470,10 +46470,10 @@
         <v>2.743851020782188</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.881868396700441</v>
+        <v>-4.861396972787213</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7907472377882641</v>
+        <v>0.7989358073535555</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.5899775787993873</v>
@@ -46493,10 +46493,10 @@
         <v>2.741270462124556</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.84348473414229</v>
+        <v>-4.823013310229062</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8035201441538931</v>
+        <v>0.8117087137191845</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.5515939162412361</v>
@@ -46516,10 +46516,10 @@
         <v>2.737999490969859</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.666368404107124</v>
+        <v>-4.645896980193895</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8710957050132619</v>
+        <v>0.8792842745785534</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.5515939162412361</v>
@@ -46539,10 +46539,10 @@
         <v>2.738682882731772</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.63666628013083</v>
+        <v>-4.616194856217602</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8836599463656925</v>
+        <v>0.8918485159309839</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.5560640414565494</v>
@@ -46562,10 +46562,10 @@
         <v>2.732469858038186</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.457290858892063</v>
+        <v>-4.436819434978834</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9491970901676139</v>
+        <v>0.9573856597329053</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.3992872832858307</v>
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.750553060213925</v>
+        <v>3.750807456499739</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.713277313369776</v>
+        <v>2.716631451908613</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.463064214317029</v>
+        <v>-4.322036818649408</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9276952033292172</v>
+        <v>0.9874603001351026</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.4191641935794213</v>
+        <v>-0.2970598579798313</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.461778797222124</v>
+        <v>2.538395537120715</v>
       </c>
     </row>
   </sheetData>
